--- a/Physics_Labs/1_sem/Lab111/Лаба 1.1.1.xlsx
+++ b/Physics_Labs/1_sem/Lab111/Лаба 1.1.1.xlsx
@@ -1,18 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10609"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alex/git/Labs/Physics_Labs/1_sem/Lab111/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71187A4B-EF8E-CD42-BC9D-6F040F2A2208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
+    <workbookView xWindow="2160" yWindow="760" windowWidth="25900" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
-    <sheet name="Sheet 2" sheetId="2" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet 2" sheetId="2" r:id="rId2"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="55">
   <si>
     <t>Основные характеристики приборов</t>
   </si>
@@ -131,9 +153,6 @@
     <t>I, мА</t>
   </si>
   <si>
-    <t>V, дел, 2мВ/дел</t>
-  </si>
-  <si>
     <t>I, дел, 0,5мА/дел</t>
   </si>
   <si>
@@ -177,17 +196,23 @@
   </si>
   <si>
     <t>+-</t>
+  </si>
+  <si>
+    <t>Параметр</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="0" formatCode="General"/>
-  </numFmts>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color indexed="8"/>
       <name val="Calibri"/>
@@ -195,18 +220,8 @@
     <font>
       <sz val="12"/>
       <color indexed="8"/>
-      <name val="Helvetica"/>
-    </font>
-    <font>
-      <sz val="15"/>
-      <color indexed="8"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1196,326 +1211,125 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+  </cellStyleXfs>
+  <cellXfs count="106">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-  </cellStyleXfs>
-  <cellXfs count="105">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="53" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="57" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="58" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="61" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="13" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="16" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="17" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="18" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="17" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="19" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="21" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="22" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="24" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="25" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="25" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="26" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="27" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="28" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="29" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="30" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="31" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="32" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="33" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="34" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="35" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="36" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="37" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="38" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="38" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="39" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="40" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="41" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="42" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="29" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="44" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="44" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="45" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="45" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="46" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="46" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="47" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="48" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="25" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="49" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="50" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="24" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="41" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="51" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="42" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="51" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="27" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="42" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="52" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="32" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="54" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="55" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="51" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="56" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="52" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="53" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="57" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="58" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="59" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="60" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="61" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="62" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="63" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1524,29 +1338,85 @@
   <tableStyles count="0"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ffff0000"/>
-      <rgbColor rgb="ff00ff00"/>
-      <rgbColor rgb="ff0000ff"/>
-      <rgbColor rgb="ffffff00"/>
-      <rgbColor rgb="ffff00ff"/>
-      <rgbColor rgb="ff00ffff"/>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffaaaaaa"/>
-      <rgbColor rgb="ff515151"/>
-      <rgbColor rgb="ffed7d31"/>
-      <rgbColor rgb="ffbdc0bf"/>
-      <rgbColor rgb="ffa5a5a5"/>
-      <rgbColor rgb="ff3f3f3f"/>
-      <rgbColor rgb="ffdbdbdb"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFAAAAAA"/>
+      <rgbColor rgb="FF515151"/>
+      <rgbColor rgb="FFED7D31"/>
+      <rgbColor rgb="FFBDC0BF"/>
+      <rgbColor rgb="FFA5A5A5"/>
+      <rgbColor rgb="FF3F3F3F"/>
+      <rgbColor rgb="FFDBDBDB"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office Theme">
       <a:dk1>
@@ -1748,7 +1618,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1767,7 +1637,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1797,7 +1667,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1823,7 +1693,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1849,7 +1719,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1875,7 +1745,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1901,7 +1771,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1927,7 +1797,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1953,7 +1823,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1979,7 +1849,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2005,7 +1875,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2018,9 +1888,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:spDef>
@@ -2037,7 +1913,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:noAutofit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -2056,7 +1932,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2082,7 +1958,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2108,7 +1984,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2134,7 +2010,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2160,7 +2036,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2186,7 +2062,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2212,7 +2088,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2238,7 +2114,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2264,7 +2140,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2290,7 +2166,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2303,9 +2179,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:lnDef>
@@ -2319,7 +2201,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -2338,7 +2220,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2368,7 +2250,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2394,7 +2276,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2420,7 +2302,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2446,7 +2328,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2472,7 +2354,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2498,7 +2380,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2524,7 +2406,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2550,7 +2432,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2576,7 +2458,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2589,45 +2471,44 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:txDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:T62"/>
-  <sheetFormatPr defaultColWidth="10.7143" defaultRowHeight="15.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:IV62"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.7344" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.2891" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.7344" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7344" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.7344" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5781" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5781" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.7344" style="1" customWidth="1"/>
-    <col min="9" max="9" width="10.7344" style="1" customWidth="1"/>
-    <col min="10" max="10" width="15.1562" style="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5469" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7344" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7344" style="1" customWidth="1"/>
-    <col min="14" max="14" width="24.375" style="1" customWidth="1"/>
-    <col min="15" max="15" width="19.3672" style="1" customWidth="1"/>
-    <col min="16" max="16" width="16.2891" style="1" customWidth="1"/>
-    <col min="17" max="17" width="10.7344" style="1" customWidth="1"/>
-    <col min="18" max="18" width="10.7344" style="1" customWidth="1"/>
-    <col min="19" max="19" width="10.7344" style="1" customWidth="1"/>
-    <col min="20" max="20" width="10.7344" style="1" customWidth="1"/>
-    <col min="21" max="256" width="10.7344" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" style="1" customWidth="1"/>
+    <col min="4" max="5" width="10.6640625" style="1" customWidth="1"/>
+    <col min="6" max="7" width="14.5" style="1" customWidth="1"/>
+    <col min="8" max="9" width="10.6640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="15.1640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5" style="1" customWidth="1"/>
+    <col min="12" max="13" width="10.6640625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="24.33203125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="19.33203125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="16.33203125" style="1" customWidth="1"/>
+    <col min="17" max="256" width="10.6640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17" customHeight="1">
+    <row r="1" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2649,7 +2530,7 @@
       <c r="S1" s="2"/>
       <c r="T1" s="2"/>
     </row>
-    <row r="2" ht="17.5" customHeight="1">
+    <row r="2" spans="1:20" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -2663,7 +2544,7 @@
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
-      <c r="N2" t="s" s="4">
+      <c r="N2" s="4" t="s">
         <v>0</v>
       </c>
       <c r="O2" s="5"/>
@@ -2673,9 +2554,9 @@
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
     </row>
-    <row r="3" ht="18" customHeight="1">
+    <row r="3" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6"/>
-      <c r="B3" t="s" s="7">
+      <c r="B3" s="7" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="8">
@@ -2701,21 +2582,23 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
-      <c r="N3" s="10"/>
-      <c r="O3" t="s" s="11">
+      <c r="N3" s="105" t="s">
+        <v>54</v>
+      </c>
+      <c r="O3" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="P3" t="s" s="12">
+      <c r="P3" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="Q3" s="13"/>
+      <c r="Q3" s="12"/>
       <c r="R3" s="2"/>
       <c r="S3" s="2"/>
       <c r="T3" s="2"/>
     </row>
-    <row r="4" ht="17.5" customHeight="1">
+    <row r="4" spans="1:20" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6"/>
-      <c r="B4" t="s" s="7">
+      <c r="B4" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="8"/>
@@ -2728,24 +2611,24 @@
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
-      <c r="M4" s="14"/>
-      <c r="N4" t="s" s="15">
+      <c r="M4" s="13"/>
+      <c r="N4" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="O4" t="s" s="16">
+      <c r="O4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="P4" t="s" s="17">
+      <c r="P4" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="Q4" s="13"/>
+      <c r="Q4" s="12"/>
       <c r="R4" s="2"/>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
     </row>
-    <row r="5" ht="17" customHeight="1">
+    <row r="5" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6"/>
-      <c r="B5" t="s" s="7">
+      <c r="B5" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C5" s="8"/>
@@ -2758,22 +2641,22 @@
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
-      <c r="M5" s="14"/>
-      <c r="N5" t="s" s="18">
+      <c r="M5" s="13"/>
+      <c r="N5" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="O5" s="19">
+      <c r="O5" s="18">
         <v>0.2</v>
       </c>
-      <c r="P5" s="20"/>
-      <c r="Q5" s="13"/>
+      <c r="P5" s="19"/>
+      <c r="Q5" s="12"/>
       <c r="R5" s="2"/>
       <c r="S5" s="2"/>
       <c r="T5" s="2"/>
     </row>
-    <row r="6" ht="17" customHeight="1">
+    <row r="6" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6"/>
-      <c r="B6" t="s" s="7">
+      <c r="B6" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="8"/>
@@ -2786,22 +2669,22 @@
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
-      <c r="M6" s="14"/>
-      <c r="N6" t="s" s="18">
+      <c r="M6" s="13"/>
+      <c r="N6" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="O6" s="19">
+      <c r="O6" s="18">
         <v>1.5</v>
       </c>
-      <c r="P6" s="20"/>
-      <c r="Q6" s="13"/>
+      <c r="P6" s="19"/>
+      <c r="Q6" s="12"/>
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
     </row>
-    <row r="7" ht="17" customHeight="1">
+    <row r="7" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6"/>
-      <c r="B7" t="s" s="7">
+      <c r="B7" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="8"/>
@@ -2814,48 +2697,48 @@
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
-      <c r="M7" s="14"/>
-      <c r="N7" t="s" s="18">
+      <c r="M7" s="13"/>
+      <c r="N7" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="O7" s="19">
+      <c r="O7" s="18">
         <v>150</v>
       </c>
-      <c r="P7" s="20"/>
-      <c r="Q7" s="13"/>
+      <c r="P7" s="19"/>
+      <c r="Q7" s="12"/>
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
       <c r="T7" s="2"/>
     </row>
-    <row r="8" ht="17" customHeight="1">
+    <row r="8" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="21"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
-      <c r="M8" s="14"/>
-      <c r="N8" t="s" s="18">
+      <c r="M8" s="13"/>
+      <c r="N8" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="O8" s="19">
+      <c r="O8" s="18">
         <v>0.01</v>
       </c>
-      <c r="P8" s="20"/>
-      <c r="Q8" s="13"/>
+      <c r="P8" s="19"/>
+      <c r="Q8" s="12"/>
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
       <c r="T8" s="2"/>
     </row>
-    <row r="9" ht="17" customHeight="1">
+    <row r="9" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
-      <c r="B9" t="s" s="22">
+      <c r="B9" s="21" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="3"/>
@@ -2868,25 +2751,25 @@
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
-      <c r="M9" s="14"/>
-      <c r="N9" t="s" s="18">
+      <c r="M9" s="13"/>
+      <c r="N9" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="O9" s="19">
+      <c r="O9" s="18">
         <v>100</v>
       </c>
-      <c r="P9" s="20"/>
-      <c r="Q9" s="13"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="12"/>
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
       <c r="T9" s="2"/>
     </row>
-    <row r="10" ht="17" customHeight="1">
+    <row r="10" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6"/>
-      <c r="B10" t="s" s="7">
+      <c r="B10" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C10" t="s" s="7">
+      <c r="C10" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D10" s="9"/>
@@ -2898,24 +2781,24 @@
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
-      <c r="M10" s="14"/>
-      <c r="N10" t="s" s="18">
+      <c r="M10" s="13"/>
+      <c r="N10" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="O10" s="19">
+      <c r="O10" s="18">
         <v>3</v>
       </c>
-      <c r="P10" s="23">
+      <c r="P10" s="22">
         <v>0.75</v>
       </c>
-      <c r="Q10" s="13"/>
+      <c r="Q10" s="12"/>
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
       <c r="T10" s="2"/>
     </row>
-    <row r="11" ht="17.5" customHeight="1">
+    <row r="11" spans="1:20" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6"/>
-      <c r="B11" t="s" s="7">
+      <c r="B11" s="7" t="s">
         <v>19</v>
       </c>
       <c r="C11" s="8">
@@ -2930,24 +2813,24 @@
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
-      <c r="M11" s="14"/>
-      <c r="N11" t="s" s="24">
+      <c r="M11" s="13"/>
+      <c r="N11" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="O11" s="25">
+      <c r="O11" s="24">
         <v>10000</v>
       </c>
-      <c r="P11" s="26">
+      <c r="P11" s="25">
         <v>1.2</v>
       </c>
-      <c r="Q11" s="13"/>
+      <c r="Q11" s="12"/>
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
     </row>
-    <row r="12" ht="17.5" customHeight="1">
+    <row r="12" spans="1:20" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6"/>
-      <c r="B12" t="s" s="7">
+      <c r="B12" s="7" t="s">
         <v>21</v>
       </c>
       <c r="C12" s="8">
@@ -2963,18 +2846,18 @@
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
-      <c r="N12" s="27"/>
-      <c r="O12" s="27"/>
-      <c r="P12" s="27"/>
+      <c r="N12" s="26"/>
+      <c r="O12" s="26"/>
+      <c r="P12" s="26"/>
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
     </row>
-    <row r="13" ht="17" customHeight="1">
+    <row r="13" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
@@ -2993,9 +2876,9 @@
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
     </row>
-    <row r="14" ht="17" customHeight="1">
+    <row r="14" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
-      <c r="B14" t="s" s="22">
+      <c r="B14" s="21" t="s">
         <v>22</v>
       </c>
       <c r="C14" s="3"/>
@@ -3017,7 +2900,7 @@
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
     </row>
-    <row r="15" ht="17" customHeight="1">
+    <row r="15" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6"/>
       <c r="B15" s="8"/>
       <c r="C15" s="8">
@@ -3059,9 +2942,9 @@
       <c r="S15" s="2"/>
       <c r="T15" s="2"/>
     </row>
-    <row r="16" ht="17" customHeight="1">
+    <row r="16" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6"/>
-      <c r="B16" t="s" s="7">
+      <c r="B16" s="7" t="s">
         <v>23</v>
       </c>
       <c r="C16" s="8">
@@ -3103,9 +2986,9 @@
       <c r="S16" s="2"/>
       <c r="T16" s="2"/>
     </row>
-    <row r="17" ht="17" customHeight="1">
+    <row r="17" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6"/>
-      <c r="B17" t="s" s="7">
+      <c r="B17" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C17" s="8">
@@ -3147,48 +3030,48 @@
       <c r="S17" s="2"/>
       <c r="T17" s="2"/>
     </row>
-    <row r="18" ht="17.5" customHeight="1">
+    <row r="18" spans="1:20" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
-      <c r="B18" s="21"/>
-      <c r="C18" s="28">
+      <c r="B18" s="20"/>
+      <c r="C18" s="27">
         <f>C17-$G19</f>
-        <v>0.01499999999999996</v>
-      </c>
-      <c r="D18" s="28">
-        <f>D17-$G19</f>
-        <v>-0.01500000000000001</v>
-      </c>
-      <c r="E18" s="28">
-        <f>E17-$G19</f>
-        <v>-0.01500000000000001</v>
-      </c>
-      <c r="F18" s="28">
-        <f>F17-$G19</f>
-        <v>-0.005000000000000004</v>
-      </c>
-      <c r="G18" s="28">
-        <f>G17-$G19</f>
-        <v>0.01499999999999996</v>
-      </c>
-      <c r="H18" s="29">
-        <f>H17-$G19</f>
-        <v>0.004999999999999949</v>
-      </c>
-      <c r="I18" s="29">
-        <f>I17-$G19</f>
-        <v>0.004999999999999949</v>
-      </c>
-      <c r="J18" s="29">
-        <f>J17-$G19</f>
-        <v>-0.005000000000000004</v>
-      </c>
-      <c r="K18" s="29">
-        <f>K17-$G19</f>
-        <v>0.004999999999999949</v>
-      </c>
-      <c r="L18" s="29">
-        <f>L17-$G19</f>
-        <v>-0.005000000000000004</v>
+        <v>1.4999999999999958E-2</v>
+      </c>
+      <c r="D18" s="27">
+        <f t="shared" ref="C18:L18" si="0">D17-$G19</f>
+        <v>-1.5000000000000013E-2</v>
+      </c>
+      <c r="E18" s="27">
+        <f t="shared" si="0"/>
+        <v>-1.5000000000000013E-2</v>
+      </c>
+      <c r="F18" s="27">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000044E-3</v>
+      </c>
+      <c r="G18" s="27">
+        <f t="shared" si="0"/>
+        <v>1.4999999999999958E-2</v>
+      </c>
+      <c r="H18" s="28">
+        <f t="shared" si="0"/>
+        <v>4.9999999999999489E-3</v>
+      </c>
+      <c r="I18" s="28">
+        <f t="shared" si="0"/>
+        <v>4.9999999999999489E-3</v>
+      </c>
+      <c r="J18" s="28">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000044E-3</v>
+      </c>
+      <c r="K18" s="28">
+        <f t="shared" si="0"/>
+        <v>4.9999999999999489E-3</v>
+      </c>
+      <c r="L18" s="28">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000044E-3</v>
       </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
@@ -3199,25 +3082,25 @@
       <c r="S18" s="2"/>
       <c r="T18" s="2"/>
     </row>
-    <row r="19" ht="17" customHeight="1">
+    <row r="19" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
-      <c r="B19" s="14"/>
-      <c r="C19" t="s" s="11">
+      <c r="B19" s="13"/>
+      <c r="C19" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="29">
         <f>SUM(C16:L16)/10</f>
-        <v>0.4</v>
-      </c>
-      <c r="E19" s="31"/>
-      <c r="F19" t="s" s="11">
+        <v>0.39999999999999997</v>
+      </c>
+      <c r="E19" s="30"/>
+      <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="G19" s="30">
+      <c r="G19" s="29">
         <f>AVERAGE(C17:L17)</f>
-        <v>0.345</v>
-      </c>
-      <c r="H19" s="13"/>
+        <v>0.34500000000000003</v>
+      </c>
+      <c r="H19" s="12"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -3231,48 +3114,48 @@
       <c r="S19" s="2"/>
       <c r="T19" s="2"/>
     </row>
-    <row r="20" ht="17" customHeight="1">
+    <row r="20" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
-      <c r="C20" s="32">
+      <c r="C20" s="31">
         <f>C18*C18</f>
-        <v>0.0002249999999999987</v>
-      </c>
-      <c r="D20" s="32">
-        <f>D18*D18</f>
-        <v>0.0002250000000000004</v>
-      </c>
-      <c r="E20" s="32">
-        <f>E18*E18</f>
-        <v>0.0002250000000000004</v>
-      </c>
-      <c r="F20" s="32">
-        <f>F18*F18</f>
-        <v>2.500000000000005e-05</v>
-      </c>
-      <c r="G20" s="32">
-        <f>G18*G18</f>
-        <v>0.0002249999999999987</v>
-      </c>
-      <c r="H20" s="33">
-        <f>H18*H18</f>
-        <v>2.499999999999949e-05</v>
-      </c>
-      <c r="I20" s="33">
-        <f>I18*I18</f>
-        <v>2.499999999999949e-05</v>
-      </c>
-      <c r="J20" s="33">
-        <f>J18*J18</f>
-        <v>2.500000000000005e-05</v>
-      </c>
-      <c r="K20" s="33">
-        <f>K18*K18</f>
-        <v>2.499999999999949e-05</v>
-      </c>
-      <c r="L20" s="33">
-        <f>L18*L18</f>
-        <v>2.500000000000005e-05</v>
+        <v>2.2499999999999875E-4</v>
+      </c>
+      <c r="D20" s="31">
+        <f t="shared" ref="C20:L20" si="1">D18*D18</f>
+        <v>2.250000000000004E-4</v>
+      </c>
+      <c r="E20" s="31">
+        <f t="shared" si="1"/>
+        <v>2.250000000000004E-4</v>
+      </c>
+      <c r="F20" s="31">
+        <f t="shared" si="1"/>
+        <v>2.5000000000000045E-5</v>
+      </c>
+      <c r="G20" s="31">
+        <f t="shared" si="1"/>
+        <v>2.2499999999999875E-4</v>
+      </c>
+      <c r="H20" s="32">
+        <f t="shared" si="1"/>
+        <v>2.499999999999949E-5</v>
+      </c>
+      <c r="I20" s="32">
+        <f t="shared" si="1"/>
+        <v>2.499999999999949E-5</v>
+      </c>
+      <c r="J20" s="32">
+        <f t="shared" si="1"/>
+        <v>2.5000000000000045E-5</v>
+      </c>
+      <c r="K20" s="32">
+        <f t="shared" si="1"/>
+        <v>2.499999999999949E-5</v>
+      </c>
+      <c r="L20" s="32">
+        <f t="shared" si="1"/>
+        <v>2.5000000000000045E-5</v>
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
@@ -3283,15 +3166,15 @@
       <c r="S20" s="2"/>
       <c r="T20" s="2"/>
     </row>
-    <row r="21" ht="17" customHeight="1">
+    <row r="21" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
-      <c r="C21" t="s" s="4">
+      <c r="C21" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D21" s="34">
+      <c r="D21" s="33">
         <f>SQRT(SUM(C20:L20))/10</f>
-        <v>0.003240370349203926</v>
+        <v>3.2403703492039256E-3</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
@@ -3310,15 +3193,15 @@
       <c r="S21" s="2"/>
       <c r="T21" s="2"/>
     </row>
-    <row r="22" ht="17" customHeight="1">
+    <row r="22" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
-      <c r="C22" t="s" s="4">
+      <c r="C22" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D22" s="34">
+      <c r="D22" s="33">
         <f>SQRT(C12*C12+D21*D21)</f>
-        <v>0.01051189802081432</v>
+        <v>1.0511898020814318E-2</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
@@ -3337,15 +3220,15 @@
       <c r="S22" s="2"/>
       <c r="T22" s="2"/>
     </row>
-    <row r="23" ht="17" customHeight="1">
+    <row r="23" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
-      <c r="C23" t="s" s="4">
+      <c r="C23" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D23" s="34">
+      <c r="D23" s="33">
         <f>(PI()*(G19*0.01*(G19*0.01))/4)</f>
-        <v>9.34820163983813e-06</v>
+        <v>9.34820163983813E-6</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
@@ -3364,15 +3247,15 @@
       <c r="S23" s="2"/>
       <c r="T23" s="2"/>
     </row>
-    <row r="24" ht="17" customHeight="1">
+    <row r="24" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
-      <c r="C24" t="s" s="4">
+      <c r="C24" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D24" s="34">
+      <c r="D24" s="33">
         <f>2*(C12/G19)*D23</f>
-        <v>5.419247327442393e-07</v>
+        <v>5.4192473274423934E-7</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
@@ -3391,7 +3274,7 @@
       <c r="S24" s="2"/>
       <c r="T24" s="2"/>
     </row>
-    <row r="25" ht="17" customHeight="1">
+    <row r="25" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -3413,7 +3296,7 @@
       <c r="S25" s="2"/>
       <c r="T25" s="2"/>
     </row>
-    <row r="26" ht="17" customHeight="1">
+    <row r="26" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -3435,7 +3318,7 @@
       <c r="S26" s="2"/>
       <c r="T26" s="2"/>
     </row>
-    <row r="27" ht="17" customHeight="1">
+    <row r="27" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -3457,7 +3340,7 @@
       <c r="S27" s="2"/>
       <c r="T27" s="2"/>
     </row>
-    <row r="28" ht="17" customHeight="1">
+    <row r="28" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -3479,7 +3362,7 @@
       <c r="S28" s="2"/>
       <c r="T28" s="2"/>
     </row>
-    <row r="29" ht="17" customHeight="1">
+    <row r="29" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -3501,9 +3384,9 @@
       <c r="S29" s="2"/>
       <c r="T29" s="2"/>
     </row>
-    <row r="30" ht="17.5" customHeight="1">
+    <row r="30" spans="1:20" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2"/>
-      <c r="B30" t="s" s="35">
+      <c r="B30" s="34" t="s">
         <v>31</v>
       </c>
       <c r="C30" s="5"/>
@@ -3525,73 +3408,73 @@
       <c r="S30" s="2"/>
       <c r="T30" s="2"/>
     </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="14"/>
-      <c r="B31" t="s" s="36">
+    <row r="31" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="13"/>
+      <c r="B31" s="102" t="s">
         <v>32</v>
       </c>
-      <c r="C31" s="37"/>
-      <c r="D31" s="37"/>
-      <c r="E31" s="38"/>
-      <c r="F31" t="s" s="36">
+      <c r="C31" s="103"/>
+      <c r="D31" s="103"/>
+      <c r="E31" s="104"/>
+      <c r="F31" s="102" t="s">
         <v>33</v>
       </c>
-      <c r="G31" s="37"/>
-      <c r="H31" s="37"/>
-      <c r="I31" s="38"/>
-      <c r="J31" t="s" s="36">
+      <c r="G31" s="103"/>
+      <c r="H31" s="103"/>
+      <c r="I31" s="104"/>
+      <c r="J31" s="102" t="s">
         <v>34</v>
       </c>
-      <c r="K31" s="37"/>
-      <c r="L31" s="37"/>
-      <c r="M31" s="38"/>
-      <c r="N31" s="39"/>
-      <c r="O31" s="40"/>
-      <c r="P31" s="40"/>
-      <c r="Q31" s="40"/>
-      <c r="R31" s="40"/>
-      <c r="S31" s="40"/>
-      <c r="T31" s="40"/>
-    </row>
-    <row r="32" ht="17" customHeight="1">
-      <c r="A32" s="14"/>
-      <c r="B32" t="s" s="11">
+      <c r="K31" s="103"/>
+      <c r="L31" s="103"/>
+      <c r="M31" s="104"/>
+      <c r="N31" s="35"/>
+      <c r="O31" s="36"/>
+      <c r="P31" s="36"/>
+      <c r="Q31" s="36"/>
+      <c r="R31" s="36"/>
+      <c r="S31" s="36"/>
+      <c r="T31" s="36"/>
+    </row>
+    <row r="32" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="13"/>
+      <c r="B32" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C32" t="s" s="41">
+      <c r="C32" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="D32" t="s" s="41">
+      <c r="D32" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="E32" t="s" s="12">
+      <c r="E32" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F32" t="s" s="11">
+      <c r="F32" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G32" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="H32" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="I32" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="J32" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="K32" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="G32" t="s" s="41">
-        <v>36</v>
-      </c>
-      <c r="H32" t="s" s="41">
+      <c r="L32" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="I32" t="s" s="12">
+      <c r="M32" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="J32" t="s" s="11">
-        <v>39</v>
-      </c>
-      <c r="K32" t="s" s="41">
-        <v>40</v>
-      </c>
-      <c r="L32" t="s" s="41">
-        <v>37</v>
-      </c>
-      <c r="M32" t="s" s="12">
-        <v>38</v>
-      </c>
-      <c r="N32" s="42"/>
+      <c r="N32" s="38"/>
       <c r="O32" s="4"/>
       <c r="P32" s="4"/>
       <c r="Q32" s="4"/>
@@ -3599,536 +3482,536 @@
       <c r="S32" s="4"/>
       <c r="T32" s="4"/>
     </row>
-    <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="14"/>
-      <c r="B33" s="43">
+    <row r="33" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="13"/>
+      <c r="B33" s="39">
         <v>30</v>
       </c>
-      <c r="C33" s="44"/>
-      <c r="D33" s="45">
-        <f>B33*10</f>
+      <c r="C33" s="40"/>
+      <c r="D33" s="41">
+        <f t="shared" ref="D33:D44" si="2">B33*10</f>
         <v>300</v>
       </c>
-      <c r="E33" s="46">
-        <v>140.67</v>
-      </c>
-      <c r="F33" s="43">
+      <c r="E33" s="42">
+        <v>140.66999999999999</v>
+      </c>
+      <c r="F33" s="39">
         <v>30</v>
       </c>
-      <c r="G33" s="44"/>
-      <c r="H33" s="45">
-        <f>F33*10</f>
+      <c r="G33" s="40"/>
+      <c r="H33" s="41">
+        <f t="shared" ref="H33:H44" si="3">F33*10</f>
         <v>300</v>
       </c>
-      <c r="I33" s="46">
+      <c r="I33" s="42">
         <v>95.34</v>
       </c>
-      <c r="J33" s="43">
+      <c r="J33" s="39">
         <v>30</v>
       </c>
-      <c r="K33" s="44"/>
-      <c r="L33" s="45">
-        <f>J33*10</f>
+      <c r="K33" s="40"/>
+      <c r="L33" s="41">
+        <f t="shared" ref="L33:L44" si="4">J33*10</f>
         <v>300</v>
       </c>
-      <c r="M33" s="46">
+      <c r="M33" s="42">
         <v>57.25</v>
       </c>
-      <c r="N33" s="47"/>
-      <c r="O33" s="34"/>
-      <c r="P33" s="34"/>
-      <c r="Q33" s="34"/>
-      <c r="R33" s="34"/>
-      <c r="S33" s="34"/>
-      <c r="T33" s="34"/>
-    </row>
-    <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="14"/>
-      <c r="B34" s="48">
+      <c r="N33" s="43"/>
+      <c r="O33" s="33"/>
+      <c r="P33" s="33"/>
+      <c r="Q33" s="33"/>
+      <c r="R33" s="33"/>
+      <c r="S33" s="33"/>
+      <c r="T33" s="33"/>
+    </row>
+    <row r="34" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="13"/>
+      <c r="B34" s="44">
         <v>56</v>
       </c>
-      <c r="C34" s="49"/>
+      <c r="C34" s="45"/>
       <c r="D34" s="8">
-        <f>B34*10</f>
+        <f t="shared" si="2"/>
         <v>560</v>
       </c>
-      <c r="E34" s="50">
+      <c r="E34" s="46">
         <v>268.27</v>
       </c>
-      <c r="F34" s="48">
+      <c r="F34" s="44">
         <v>54</v>
       </c>
-      <c r="G34" s="49"/>
+      <c r="G34" s="45"/>
       <c r="H34" s="8">
-        <f>F34*10</f>
+        <f t="shared" si="3"/>
         <v>540</v>
       </c>
-      <c r="I34" s="50">
+      <c r="I34" s="46">
         <v>174.57</v>
       </c>
-      <c r="J34" s="48">
+      <c r="J34" s="44">
         <v>55</v>
       </c>
-      <c r="K34" s="49"/>
+      <c r="K34" s="45"/>
       <c r="L34" s="8">
-        <f>J34*10</f>
+        <f t="shared" si="4"/>
         <v>550</v>
       </c>
-      <c r="M34" s="50">
+      <c r="M34" s="46">
         <v>105.06</v>
       </c>
-      <c r="N34" s="47"/>
-      <c r="O34" s="34"/>
-      <c r="P34" s="34"/>
-      <c r="Q34" s="34"/>
-      <c r="R34" s="34"/>
-      <c r="S34" s="34"/>
-      <c r="T34" s="34"/>
-    </row>
-    <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="14"/>
-      <c r="B35" s="48">
+      <c r="N34" s="43"/>
+      <c r="O34" s="33"/>
+      <c r="P34" s="33"/>
+      <c r="Q34" s="33"/>
+      <c r="R34" s="33"/>
+      <c r="S34" s="33"/>
+      <c r="T34" s="33"/>
+    </row>
+    <row r="35" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="13"/>
+      <c r="B35" s="44">
         <v>72</v>
       </c>
-      <c r="C35" s="49"/>
+      <c r="C35" s="45"/>
       <c r="D35" s="8">
-        <f>B35*10</f>
+        <f t="shared" si="2"/>
         <v>720</v>
       </c>
-      <c r="E35" s="50">
+      <c r="E35" s="46">
         <v>345.68</v>
       </c>
-      <c r="F35" s="48">
+      <c r="F35" s="44">
         <v>61</v>
       </c>
-      <c r="G35" s="49"/>
+      <c r="G35" s="45"/>
       <c r="H35" s="8">
-        <f>F35*10</f>
+        <f t="shared" si="3"/>
         <v>610</v>
       </c>
-      <c r="I35" s="50">
+      <c r="I35" s="46">
         <v>193.8</v>
       </c>
-      <c r="J35" s="48">
+      <c r="J35" s="44">
         <v>57</v>
       </c>
-      <c r="K35" s="49"/>
+      <c r="K35" s="45"/>
       <c r="L35" s="8">
-        <f>J35*10</f>
+        <f t="shared" si="4"/>
         <v>570</v>
       </c>
-      <c r="M35" s="50">
+      <c r="M35" s="46">
         <v>110.27</v>
       </c>
-      <c r="N35" s="47"/>
-      <c r="O35" s="34"/>
-      <c r="P35" s="34"/>
-      <c r="Q35" s="34"/>
-      <c r="R35" s="34"/>
-      <c r="S35" s="34"/>
-      <c r="T35" s="34"/>
-    </row>
-    <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="14"/>
-      <c r="B36" s="48">
+      <c r="N35" s="43"/>
+      <c r="O35" s="33"/>
+      <c r="P35" s="33"/>
+      <c r="Q35" s="33"/>
+      <c r="R35" s="33"/>
+      <c r="S35" s="33"/>
+      <c r="T35" s="33"/>
+    </row>
+    <row r="36" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="13"/>
+      <c r="B36" s="44">
         <v>74</v>
       </c>
-      <c r="C36" s="49"/>
+      <c r="C36" s="45"/>
       <c r="D36" s="8">
-        <f>B36*10</f>
+        <f t="shared" si="2"/>
         <v>740</v>
       </c>
-      <c r="E36" s="50">
+      <c r="E36" s="46">
         <v>353.54</v>
       </c>
-      <c r="F36" s="48">
+      <c r="F36" s="44">
         <v>86</v>
       </c>
-      <c r="G36" s="49"/>
+      <c r="G36" s="45"/>
       <c r="H36" s="8">
-        <f>F36*10</f>
+        <f t="shared" si="3"/>
         <v>860</v>
       </c>
-      <c r="I36" s="50">
+      <c r="I36" s="46">
         <v>274.2</v>
       </c>
-      <c r="J36" s="48">
+      <c r="J36" s="44">
         <v>79</v>
       </c>
-      <c r="K36" s="49"/>
+      <c r="K36" s="45"/>
       <c r="L36" s="8">
-        <f>J36*10</f>
+        <f t="shared" si="4"/>
         <v>790</v>
       </c>
-      <c r="M36" s="50">
-        <v>150.86</v>
-      </c>
-      <c r="N36" s="47"/>
-      <c r="O36" s="34"/>
-      <c r="P36" s="34"/>
-      <c r="Q36" s="34"/>
-      <c r="R36" s="34"/>
-      <c r="S36" s="34"/>
-      <c r="T36" s="34"/>
-    </row>
-    <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="14"/>
-      <c r="B37" s="48">
+      <c r="M36" s="46">
+        <v>150.86000000000001</v>
+      </c>
+      <c r="N36" s="43"/>
+      <c r="O36" s="33"/>
+      <c r="P36" s="33"/>
+      <c r="Q36" s="33"/>
+      <c r="R36" s="33"/>
+      <c r="S36" s="33"/>
+      <c r="T36" s="33"/>
+    </row>
+    <row r="37" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="13"/>
+      <c r="B37" s="44">
         <v>85</v>
       </c>
-      <c r="C37" s="49"/>
+      <c r="C37" s="45"/>
       <c r="D37" s="8">
-        <f>B37*10</f>
+        <f t="shared" si="2"/>
         <v>850</v>
       </c>
-      <c r="E37" s="50">
+      <c r="E37" s="46">
         <v>405.3</v>
       </c>
-      <c r="F37" s="48">
+      <c r="F37" s="44">
         <v>76</v>
       </c>
-      <c r="G37" s="49"/>
+      <c r="G37" s="45"/>
       <c r="H37" s="8">
-        <f>F37*10</f>
+        <f t="shared" si="3"/>
         <v>760</v>
       </c>
-      <c r="I37" s="50">
+      <c r="I37" s="46">
         <v>242.25</v>
       </c>
-      <c r="J37" s="48">
+      <c r="J37" s="44">
         <v>83</v>
       </c>
-      <c r="K37" s="49"/>
+      <c r="K37" s="45"/>
       <c r="L37" s="8">
-        <f>J37*10</f>
+        <f t="shared" si="4"/>
         <v>830</v>
       </c>
-      <c r="M37" s="50">
+      <c r="M37" s="46">
         <v>159.43</v>
       </c>
-      <c r="N37" s="47"/>
-      <c r="O37" s="34"/>
-      <c r="P37" s="34"/>
-      <c r="Q37" s="34"/>
-      <c r="R37" s="34"/>
-      <c r="S37" s="34"/>
-      <c r="T37" s="34"/>
-    </row>
-    <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="14"/>
-      <c r="B38" s="51">
+      <c r="N37" s="43"/>
+      <c r="O37" s="33"/>
+      <c r="P37" s="33"/>
+      <c r="Q37" s="33"/>
+      <c r="R37" s="33"/>
+      <c r="S37" s="33"/>
+      <c r="T37" s="33"/>
+    </row>
+    <row r="38" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="13"/>
+      <c r="B38" s="47">
         <v>97</v>
       </c>
-      <c r="C38" s="52"/>
-      <c r="D38" s="53">
-        <f>B38*10</f>
+      <c r="C38" s="48"/>
+      <c r="D38" s="49">
+        <f t="shared" si="2"/>
         <v>970</v>
       </c>
-      <c r="E38" s="54">
+      <c r="E38" s="50">
         <v>466.22</v>
       </c>
-      <c r="F38" s="51">
+      <c r="F38" s="47">
         <v>98</v>
       </c>
-      <c r="G38" s="52"/>
-      <c r="H38" s="53">
-        <f>F38*10</f>
+      <c r="G38" s="48"/>
+      <c r="H38" s="49">
+        <f t="shared" si="3"/>
         <v>980</v>
       </c>
-      <c r="I38" s="54">
+      <c r="I38" s="50">
         <v>315.37</v>
       </c>
-      <c r="J38" s="51">
+      <c r="J38" s="47">
         <v>92</v>
       </c>
-      <c r="K38" s="52"/>
-      <c r="L38" s="53">
-        <f>J38*10</f>
+      <c r="K38" s="48"/>
+      <c r="L38" s="49">
+        <f t="shared" si="4"/>
         <v>920</v>
       </c>
-      <c r="M38" s="54">
+      <c r="M38" s="50">
         <v>176.11</v>
       </c>
-      <c r="N38" s="47"/>
-      <c r="O38" s="34"/>
-      <c r="P38" s="34"/>
-      <c r="Q38" s="34"/>
-      <c r="R38" s="34"/>
-      <c r="S38" s="34"/>
-      <c r="T38" s="34"/>
-    </row>
-    <row r="39" ht="17" customHeight="1">
-      <c r="A39" s="14"/>
-      <c r="B39" s="43">
+      <c r="N38" s="43"/>
+      <c r="O38" s="33"/>
+      <c r="P38" s="33"/>
+      <c r="Q38" s="33"/>
+      <c r="R38" s="33"/>
+      <c r="S38" s="33"/>
+      <c r="T38" s="33"/>
+    </row>
+    <row r="39" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="13"/>
+      <c r="B39" s="39">
         <v>77</v>
       </c>
-      <c r="C39" s="44"/>
-      <c r="D39" s="45">
-        <f>B39*10</f>
+      <c r="C39" s="40"/>
+      <c r="D39" s="41">
+        <f t="shared" si="2"/>
         <v>770</v>
       </c>
-      <c r="E39" s="46">
+      <c r="E39" s="42">
         <v>371.86</v>
       </c>
-      <c r="F39" s="43">
+      <c r="F39" s="39">
         <v>79</v>
       </c>
-      <c r="G39" s="44"/>
-      <c r="H39" s="45">
-        <f>F39*10</f>
+      <c r="G39" s="40"/>
+      <c r="H39" s="41">
+        <f t="shared" si="3"/>
         <v>790</v>
       </c>
-      <c r="I39" s="46">
+      <c r="I39" s="42">
         <v>252.87</v>
       </c>
-      <c r="J39" s="43">
+      <c r="J39" s="39">
         <v>91</v>
       </c>
-      <c r="K39" s="44"/>
-      <c r="L39" s="45">
-        <f>J39*10</f>
+      <c r="K39" s="40"/>
+      <c r="L39" s="41">
+        <f t="shared" si="4"/>
         <v>910</v>
       </c>
-      <c r="M39" s="46">
+      <c r="M39" s="42">
         <v>174.3</v>
       </c>
-      <c r="N39" s="47"/>
-      <c r="O39" s="34"/>
-      <c r="P39" s="34"/>
-      <c r="Q39" s="34"/>
-      <c r="R39" s="34"/>
-      <c r="S39" s="34"/>
-      <c r="T39" s="34"/>
-    </row>
-    <row r="40" ht="17" customHeight="1">
-      <c r="A40" s="14"/>
-      <c r="B40" s="48">
+      <c r="N39" s="43"/>
+      <c r="O39" s="33"/>
+      <c r="P39" s="33"/>
+      <c r="Q39" s="33"/>
+      <c r="R39" s="33"/>
+      <c r="S39" s="33"/>
+      <c r="T39" s="33"/>
+    </row>
+    <row r="40" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="13"/>
+      <c r="B40" s="44">
         <v>68</v>
       </c>
-      <c r="C40" s="49"/>
+      <c r="C40" s="45"/>
       <c r="D40" s="8">
-        <f>B40*10</f>
+        <f t="shared" si="2"/>
         <v>680</v>
       </c>
-      <c r="E40" s="50">
+      <c r="E40" s="46">
         <v>326.31</v>
       </c>
-      <c r="F40" s="48">
+      <c r="F40" s="44">
         <v>61</v>
       </c>
-      <c r="G40" s="49"/>
+      <c r="G40" s="45"/>
       <c r="H40" s="8">
-        <f>F40*10</f>
+        <f t="shared" si="3"/>
         <v>610</v>
       </c>
-      <c r="I40" s="50">
+      <c r="I40" s="46">
         <v>196.32</v>
       </c>
-      <c r="J40" s="48">
+      <c r="J40" s="44">
         <v>78</v>
       </c>
-      <c r="K40" s="49"/>
+      <c r="K40" s="45"/>
       <c r="L40" s="8">
-        <f>J40*10</f>
+        <f t="shared" si="4"/>
         <v>780</v>
       </c>
-      <c r="M40" s="50">
+      <c r="M40" s="46">
         <v>148.54</v>
       </c>
-      <c r="N40" s="47"/>
-      <c r="O40" s="34"/>
-      <c r="P40" s="34"/>
-      <c r="Q40" s="34"/>
-      <c r="R40" s="34"/>
-      <c r="S40" s="34"/>
-      <c r="T40" s="34"/>
-    </row>
-    <row r="41" ht="17" customHeight="1">
-      <c r="A41" s="14"/>
-      <c r="B41" s="48">
+      <c r="N40" s="43"/>
+      <c r="O40" s="33"/>
+      <c r="P40" s="33"/>
+      <c r="Q40" s="33"/>
+      <c r="R40" s="33"/>
+      <c r="S40" s="33"/>
+      <c r="T40" s="33"/>
+    </row>
+    <row r="41" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="13"/>
+      <c r="B41" s="44">
         <v>57</v>
       </c>
-      <c r="C41" s="49"/>
+      <c r="C41" s="45"/>
       <c r="D41" s="8">
-        <f>B41*10</f>
+        <f t="shared" si="2"/>
         <v>570</v>
       </c>
-      <c r="E41" s="50">
+      <c r="E41" s="46">
         <v>271.3</v>
       </c>
-      <c r="F41" s="48">
+      <c r="F41" s="44">
         <v>55</v>
       </c>
-      <c r="G41" s="49"/>
+      <c r="G41" s="45"/>
       <c r="H41" s="8">
-        <f>F41*10</f>
+        <f t="shared" si="3"/>
         <v>550</v>
       </c>
-      <c r="I41" s="50">
+      <c r="I41" s="46">
         <v>177.79</v>
       </c>
-      <c r="J41" s="48">
+      <c r="J41" s="44">
         <v>64</v>
       </c>
-      <c r="K41" s="49"/>
+      <c r="K41" s="45"/>
       <c r="L41" s="8">
-        <f>J41*10</f>
+        <f t="shared" si="4"/>
         <v>640</v>
       </c>
-      <c r="M41" s="50">
+      <c r="M41" s="46">
         <v>122.64</v>
       </c>
-      <c r="N41" s="47"/>
-      <c r="O41" s="34"/>
-      <c r="P41" s="34"/>
-      <c r="Q41" s="34"/>
-      <c r="R41" s="34"/>
-      <c r="S41" s="34"/>
-      <c r="T41" s="34"/>
-    </row>
-    <row r="42" ht="17" customHeight="1">
-      <c r="A42" s="14"/>
-      <c r="B42" s="48">
+      <c r="N41" s="43"/>
+      <c r="O41" s="33"/>
+      <c r="P41" s="33"/>
+      <c r="Q41" s="33"/>
+      <c r="R41" s="33"/>
+      <c r="S41" s="33"/>
+      <c r="T41" s="33"/>
+    </row>
+    <row r="42" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="13"/>
+      <c r="B42" s="44">
         <v>50</v>
       </c>
-      <c r="C42" s="49"/>
+      <c r="C42" s="45"/>
       <c r="D42" s="8">
-        <f>B42*10</f>
+        <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="E42" s="50">
+      <c r="E42" s="46">
         <v>241.55</v>
       </c>
-      <c r="F42" s="48">
+      <c r="F42" s="44">
         <v>47</v>
       </c>
-      <c r="G42" s="49"/>
+      <c r="G42" s="45"/>
       <c r="H42" s="8">
-        <f>F42*10</f>
+        <f t="shared" si="3"/>
         <v>470</v>
       </c>
-      <c r="I42" s="50">
+      <c r="I42" s="46">
         <v>151.28</v>
       </c>
-      <c r="J42" s="48">
+      <c r="J42" s="44">
         <v>50</v>
       </c>
-      <c r="K42" s="49"/>
+      <c r="K42" s="45"/>
       <c r="L42" s="8">
-        <f>J42*10</f>
+        <f t="shared" si="4"/>
         <v>500</v>
       </c>
-      <c r="M42" s="50">
+      <c r="M42" s="46">
         <v>96.53</v>
       </c>
-      <c r="N42" s="47"/>
-      <c r="O42" s="34"/>
-      <c r="P42" s="34"/>
-      <c r="Q42" s="34"/>
-      <c r="R42" s="34"/>
-      <c r="S42" s="34"/>
-      <c r="T42" s="34"/>
-    </row>
-    <row r="43" ht="17" customHeight="1">
-      <c r="A43" s="14"/>
-      <c r="B43" s="48">
+      <c r="N42" s="43"/>
+      <c r="O42" s="33"/>
+      <c r="P42" s="33"/>
+      <c r="Q42" s="33"/>
+      <c r="R42" s="33"/>
+      <c r="S42" s="33"/>
+      <c r="T42" s="33"/>
+    </row>
+    <row r="43" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="13"/>
+      <c r="B43" s="44">
         <v>42</v>
       </c>
-      <c r="C43" s="49"/>
+      <c r="C43" s="45"/>
       <c r="D43" s="8">
-        <f>B43*10</f>
+        <f t="shared" si="2"/>
         <v>420</v>
       </c>
-      <c r="E43" s="50">
+      <c r="E43" s="46">
         <v>201.16</v>
       </c>
-      <c r="F43" s="48">
+      <c r="F43" s="44">
         <v>37</v>
       </c>
-      <c r="G43" s="49"/>
+      <c r="G43" s="45"/>
       <c r="H43" s="8">
-        <f>F43*10</f>
+        <f t="shared" si="3"/>
         <v>370</v>
       </c>
-      <c r="I43" s="50">
+      <c r="I43" s="46">
         <v>117.92</v>
       </c>
-      <c r="J43" s="48">
+      <c r="J43" s="44">
         <v>39</v>
       </c>
-      <c r="K43" s="49"/>
+      <c r="K43" s="45"/>
       <c r="L43" s="8">
-        <f>J43*10</f>
+        <f t="shared" si="4"/>
         <v>390</v>
       </c>
-      <c r="M43" s="50">
+      <c r="M43" s="46">
         <v>74.75</v>
       </c>
-      <c r="N43" s="47"/>
-      <c r="O43" s="34"/>
-      <c r="P43" s="34"/>
-      <c r="Q43" s="34"/>
-      <c r="R43" s="34"/>
-      <c r="S43" s="34"/>
-      <c r="T43" s="34"/>
-    </row>
-    <row r="44" ht="17" customHeight="1">
-      <c r="A44" s="14"/>
-      <c r="B44" s="51">
+      <c r="N43" s="43"/>
+      <c r="O43" s="33"/>
+      <c r="P43" s="33"/>
+      <c r="Q43" s="33"/>
+      <c r="R43" s="33"/>
+      <c r="S43" s="33"/>
+      <c r="T43" s="33"/>
+    </row>
+    <row r="44" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="13"/>
+      <c r="B44" s="47">
         <v>33</v>
       </c>
-      <c r="C44" s="52"/>
-      <c r="D44" s="53">
-        <f>B44*10</f>
+      <c r="C44" s="48"/>
+      <c r="D44" s="49">
+        <f t="shared" si="2"/>
         <v>330</v>
       </c>
-      <c r="E44" s="54">
+      <c r="E44" s="50">
         <v>161.18</v>
       </c>
-      <c r="F44" s="51">
+      <c r="F44" s="47">
         <v>25</v>
       </c>
-      <c r="G44" s="52"/>
-      <c r="H44" s="53">
-        <f>F44*10</f>
+      <c r="G44" s="48"/>
+      <c r="H44" s="49">
+        <f t="shared" si="3"/>
         <v>250</v>
       </c>
-      <c r="I44" s="54">
+      <c r="I44" s="50">
         <v>80.25</v>
       </c>
-      <c r="J44" s="51">
+      <c r="J44" s="47">
         <v>27</v>
       </c>
-      <c r="K44" s="52"/>
-      <c r="L44" s="53">
-        <f>J44*10</f>
+      <c r="K44" s="48"/>
+      <c r="L44" s="49">
+        <f t="shared" si="4"/>
         <v>270</v>
       </c>
-      <c r="M44" s="54">
+      <c r="M44" s="50">
         <v>50.4</v>
       </c>
-      <c r="N44" s="47"/>
-      <c r="O44" s="34"/>
-      <c r="P44" s="34"/>
-      <c r="Q44" s="34"/>
-      <c r="R44" s="34"/>
-      <c r="S44" s="34"/>
-      <c r="T44" s="34"/>
-    </row>
-    <row r="45" ht="17" customHeight="1">
+      <c r="N44" s="43"/>
+      <c r="O44" s="33"/>
+      <c r="P44" s="33"/>
+      <c r="Q44" s="33"/>
+      <c r="R44" s="33"/>
+      <c r="S44" s="33"/>
+      <c r="T44" s="33"/>
+    </row>
+    <row r="45" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="6"/>
-      <c r="B45" s="55"/>
-      <c r="C45" s="55"/>
-      <c r="D45" s="55"/>
-      <c r="E45" s="55"/>
-      <c r="F45" s="55"/>
-      <c r="G45" s="55"/>
-      <c r="H45" s="55"/>
-      <c r="I45" s="55"/>
-      <c r="J45" s="55"/>
-      <c r="K45" s="55"/>
-      <c r="L45" s="55"/>
-      <c r="M45" s="56"/>
+      <c r="B45" s="51"/>
+      <c r="C45" s="51"/>
+      <c r="D45" s="51"/>
+      <c r="E45" s="51"/>
+      <c r="F45" s="51"/>
+      <c r="G45" s="51"/>
+      <c r="H45" s="51"/>
+      <c r="I45" s="51"/>
+      <c r="J45" s="51"/>
+      <c r="K45" s="51"/>
+      <c r="L45" s="51"/>
+      <c r="M45" s="52"/>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" s="2"/>
@@ -4137,1030 +4020,1030 @@
       <c r="S45" s="2"/>
       <c r="T45" s="2"/>
     </row>
-    <row r="46" ht="17" customHeight="1">
-      <c r="A46" s="57"/>
-      <c r="B46" s="58"/>
-      <c r="C46" s="58"/>
-      <c r="D46" s="58"/>
-      <c r="E46" s="58"/>
-      <c r="F46" s="58"/>
-      <c r="G46" s="58"/>
-      <c r="H46" s="59"/>
-      <c r="I46" t="s" s="60">
+    <row r="46" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="53"/>
+      <c r="B46" s="54"/>
+      <c r="C46" s="54"/>
+      <c r="D46" s="54"/>
+      <c r="E46" s="54"/>
+      <c r="F46" s="54"/>
+      <c r="G46" s="54"/>
+      <c r="H46" s="55"/>
+      <c r="I46" s="100" t="s">
+        <v>40</v>
+      </c>
+      <c r="J46" s="101"/>
+      <c r="K46" s="55"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="55"/>
+      <c r="N46" s="55"/>
+      <c r="O46" s="55"/>
+      <c r="P46" s="55"/>
+      <c r="Q46" s="55"/>
+      <c r="R46" s="55"/>
+      <c r="S46" s="55"/>
+      <c r="T46" s="56"/>
+    </row>
+    <row r="47" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="57"/>
+      <c r="B47" s="98" t="s">
+        <v>32</v>
+      </c>
+      <c r="C47" s="99"/>
+      <c r="D47" s="98" t="s">
+        <v>33</v>
+      </c>
+      <c r="E47" s="99"/>
+      <c r="F47" s="98" t="s">
+        <v>34</v>
+      </c>
+      <c r="G47" s="99"/>
+      <c r="H47" s="59"/>
+      <c r="I47" s="60">
+        <f t="shared" ref="I47:I58" si="5">D33*E33</f>
+        <v>42200.999999999993</v>
+      </c>
+      <c r="J47" s="60">
+        <f t="shared" ref="J47:J58" si="6">(E33*E33)</f>
+        <v>19788.048899999998</v>
+      </c>
+      <c r="K47" s="60">
+        <f t="shared" ref="K47:K58" si="7">H33*I33</f>
+        <v>28602</v>
+      </c>
+      <c r="L47" s="60">
+        <f t="shared" ref="L47:L58" si="8">I33*I33</f>
+        <v>9089.7156000000014</v>
+      </c>
+      <c r="M47" s="60">
+        <f t="shared" ref="M47:M58" si="9">L33*M33</f>
+        <v>17175</v>
+      </c>
+      <c r="N47" s="60">
+        <f t="shared" ref="N47:N58" si="10">M33*M33</f>
+        <v>3277.5625</v>
+      </c>
+      <c r="O47" s="60">
+        <f t="shared" ref="O47:O58" si="11">D33*D33</f>
+        <v>90000</v>
+      </c>
+      <c r="P47" s="60">
+        <f t="shared" ref="P47:P58" si="12">E33*E33</f>
+        <v>19788.048899999998</v>
+      </c>
+      <c r="Q47" s="60">
+        <f t="shared" ref="Q47:Q58" si="13">H33*H33</f>
+        <v>90000</v>
+      </c>
+      <c r="R47" s="60">
+        <f t="shared" ref="R47:R58" si="14">I33*I33</f>
+        <v>9089.7156000000014</v>
+      </c>
+      <c r="S47" s="60">
+        <f t="shared" ref="S47:S58" si="15">L33*L33</f>
+        <v>90000</v>
+      </c>
+      <c r="T47" s="61">
+        <f t="shared" ref="T47:T58" si="16">M33*M33</f>
+        <v>3277.5625</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="57"/>
+      <c r="B48" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="J46" s="59"/>
-      <c r="K46" s="59"/>
-      <c r="L46" s="59"/>
-      <c r="M46" s="59"/>
-      <c r="N46" s="59"/>
-      <c r="O46" s="59"/>
-      <c r="P46" s="59"/>
-      <c r="Q46" s="59"/>
-      <c r="R46" s="59"/>
-      <c r="S46" s="59"/>
-      <c r="T46" s="61"/>
-    </row>
-    <row r="47" ht="17" customHeight="1">
-      <c r="A47" s="62"/>
-      <c r="B47" t="s" s="63">
-        <v>32</v>
-      </c>
-      <c r="C47" s="64"/>
-      <c r="D47" t="s" s="63">
-        <v>33</v>
-      </c>
-      <c r="E47" s="64"/>
-      <c r="F47" t="s" s="63">
-        <v>34</v>
-      </c>
-      <c r="G47" s="64"/>
-      <c r="H47" s="65"/>
-      <c r="I47" s="66">
-        <f>D33*E33</f>
-        <v>42200.999999999993</v>
-      </c>
-      <c r="J47" s="66">
-        <f>(E33*E33)</f>
-        <v>19788.0489</v>
-      </c>
-      <c r="K47" s="66">
-        <f>H33*I33</f>
-        <v>28602</v>
-      </c>
-      <c r="L47" s="66">
-        <f>I33*I33</f>
-        <v>9089.715600000001</v>
-      </c>
-      <c r="M47" s="66">
-        <f>L33*M33</f>
-        <v>17175</v>
-      </c>
-      <c r="N47" s="66">
-        <f>M33*M33</f>
-        <v>3277.5625</v>
-      </c>
-      <c r="O47" s="66">
-        <f>D33*D33</f>
-        <v>90000</v>
-      </c>
-      <c r="P47" s="66">
-        <f>E33*E33</f>
-        <v>19788.0489</v>
-      </c>
-      <c r="Q47" s="66">
-        <f>H33*H33</f>
-        <v>90000</v>
-      </c>
-      <c r="R47" s="66">
-        <f>I33*I33</f>
-        <v>9089.715600000001</v>
-      </c>
-      <c r="S47" s="66">
-        <f>L33*L33</f>
-        <v>90000</v>
-      </c>
-      <c r="T47" s="67">
-        <f>M33*M33</f>
-        <v>3277.5625</v>
-      </c>
-    </row>
-    <row r="48" ht="17" customHeight="1">
-      <c r="A48" s="62"/>
-      <c r="B48" t="s" s="68">
+      <c r="C48" s="63">
+        <v>2.06</v>
+      </c>
+      <c r="D48" s="62" t="s">
+        <v>41</v>
+      </c>
+      <c r="E48" s="63">
+        <v>3.09</v>
+      </c>
+      <c r="F48" s="62" t="s">
+        <v>41</v>
+      </c>
+      <c r="G48" s="63">
+        <v>5.1609999999999996</v>
+      </c>
+      <c r="H48" s="59"/>
+      <c r="I48" s="60">
+        <f t="shared" si="5"/>
+        <v>150231.19999999998</v>
+      </c>
+      <c r="J48" s="60">
+        <f t="shared" si="6"/>
+        <v>71968.792899999986</v>
+      </c>
+      <c r="K48" s="60">
+        <f t="shared" si="7"/>
+        <v>94267.8</v>
+      </c>
+      <c r="L48" s="60">
+        <f t="shared" si="8"/>
+        <v>30474.684899999997</v>
+      </c>
+      <c r="M48" s="60">
+        <f t="shared" si="9"/>
+        <v>57783</v>
+      </c>
+      <c r="N48" s="60">
+        <f t="shared" si="10"/>
+        <v>11037.6036</v>
+      </c>
+      <c r="O48" s="60">
+        <f t="shared" si="11"/>
+        <v>313600</v>
+      </c>
+      <c r="P48" s="60">
+        <f t="shared" si="12"/>
+        <v>71968.792899999986</v>
+      </c>
+      <c r="Q48" s="60">
+        <f t="shared" si="13"/>
+        <v>291600</v>
+      </c>
+      <c r="R48" s="60">
+        <f t="shared" si="14"/>
+        <v>30474.684899999997</v>
+      </c>
+      <c r="S48" s="60">
+        <f t="shared" si="15"/>
+        <v>302500</v>
+      </c>
+      <c r="T48" s="61">
+        <f t="shared" si="16"/>
+        <v>11037.6036</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="57"/>
+      <c r="B49" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="C48" s="69">
-        <v>2.06</v>
-      </c>
-      <c r="D48" t="s" s="68">
+      <c r="C49" s="65">
+        <f>J60</f>
+        <v>2.0852247524847378</v>
+      </c>
+      <c r="D49" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="E48" s="69">
-        <v>3.09</v>
-      </c>
-      <c r="F48" t="s" s="68">
+      <c r="E49" s="65">
+        <f>L60</f>
+        <v>3.1206369466740131</v>
+      </c>
+      <c r="F49" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="G48" s="69">
-        <v>5.161</v>
-      </c>
-      <c r="H48" s="65"/>
-      <c r="I48" s="66">
-        <f>D34*E34</f>
-        <v>150231.2</v>
-      </c>
-      <c r="J48" s="66">
-        <f>(E34*E34)</f>
-        <v>71968.792899999986</v>
-      </c>
-      <c r="K48" s="66">
-        <f>H34*I34</f>
-        <v>94267.8</v>
-      </c>
-      <c r="L48" s="66">
-        <f>I34*I34</f>
-        <v>30474.6849</v>
-      </c>
-      <c r="M48" s="66">
-        <f>L34*M34</f>
-        <v>57783</v>
-      </c>
-      <c r="N48" s="66">
-        <f>M34*M34</f>
-        <v>11037.6036</v>
-      </c>
-      <c r="O48" s="66">
-        <f>D34*D34</f>
-        <v>313600</v>
-      </c>
-      <c r="P48" s="66">
-        <f>E34*E34</f>
-        <v>71968.792899999986</v>
-      </c>
-      <c r="Q48" s="66">
-        <f>H34*H34</f>
-        <v>291600</v>
-      </c>
-      <c r="R48" s="66">
-        <f>I34*I34</f>
-        <v>30474.6849</v>
-      </c>
-      <c r="S48" s="66">
-        <f>L34*L34</f>
-        <v>302500</v>
-      </c>
-      <c r="T48" s="67">
-        <f>M34*M34</f>
-        <v>11037.6036</v>
-      </c>
-    </row>
-    <row r="49" ht="17" customHeight="1">
-      <c r="A49" s="62"/>
-      <c r="B49" t="s" s="70">
+      <c r="G49" s="65">
+        <f>N60</f>
+        <v>5.2221637862988661</v>
+      </c>
+      <c r="H49" s="59"/>
+      <c r="I49" s="60">
+        <f t="shared" si="5"/>
+        <v>248889.60000000001</v>
+      </c>
+      <c r="J49" s="60">
+        <f t="shared" si="6"/>
+        <v>119494.6624</v>
+      </c>
+      <c r="K49" s="60">
+        <f t="shared" si="7"/>
+        <v>118218</v>
+      </c>
+      <c r="L49" s="60">
+        <f t="shared" si="8"/>
+        <v>37558.44</v>
+      </c>
+      <c r="M49" s="60">
+        <f t="shared" si="9"/>
+        <v>62853.899999999994</v>
+      </c>
+      <c r="N49" s="60">
+        <f t="shared" si="10"/>
+        <v>12159.472899999999</v>
+      </c>
+      <c r="O49" s="60">
+        <f t="shared" si="11"/>
+        <v>518400</v>
+      </c>
+      <c r="P49" s="60">
+        <f t="shared" si="12"/>
+        <v>119494.6624</v>
+      </c>
+      <c r="Q49" s="60">
+        <f t="shared" si="13"/>
+        <v>372100</v>
+      </c>
+      <c r="R49" s="60">
+        <f t="shared" si="14"/>
+        <v>37558.44</v>
+      </c>
+      <c r="S49" s="60">
+        <f t="shared" si="15"/>
+        <v>324900</v>
+      </c>
+      <c r="T49" s="61">
+        <f t="shared" si="16"/>
+        <v>12159.472899999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="57"/>
+      <c r="B50" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="C49" s="71">
-        <f>J60</f>
-        <v>2.085224752484738</v>
-      </c>
-      <c r="D49" t="s" s="70">
+      <c r="C50" s="65">
+        <f>C49+(C49*C49)/O11</f>
+        <v>2.0856595687115753</v>
+      </c>
+      <c r="D50" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="E49" s="71">
-        <f>L60</f>
-        <v>3.120636946674013</v>
-      </c>
-      <c r="F49" t="s" s="70">
+      <c r="E50" s="65">
+        <f>E49+(E49*E49)/O11</f>
+        <v>3.1216107841693077</v>
+      </c>
+      <c r="F50" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="G49" s="71">
-        <f>N60</f>
-        <v>5.222163786298866</v>
-      </c>
-      <c r="H49" s="65"/>
-      <c r="I49" s="66">
-        <f>D35*E35</f>
-        <v>248889.6</v>
-      </c>
-      <c r="J49" s="66">
-        <f>(E35*E35)</f>
-        <v>119494.6624</v>
-      </c>
-      <c r="K49" s="66">
-        <f>H35*I35</f>
-        <v>118218</v>
-      </c>
-      <c r="L49" s="66">
-        <f>I35*I35</f>
-        <v>37558.44</v>
-      </c>
-      <c r="M49" s="66">
-        <f>L35*M35</f>
-        <v>62853.899999999994</v>
-      </c>
-      <c r="N49" s="66">
-        <f>M35*M35</f>
-        <v>12159.4729</v>
-      </c>
-      <c r="O49" s="66">
-        <f>D35*D35</f>
-        <v>518400</v>
-      </c>
-      <c r="P49" s="66">
-        <f>E35*E35</f>
-        <v>119494.6624</v>
-      </c>
-      <c r="Q49" s="66">
-        <f>H35*H35</f>
-        <v>372100</v>
-      </c>
-      <c r="R49" s="66">
-        <f>I35*I35</f>
-        <v>37558.44</v>
-      </c>
-      <c r="S49" s="66">
-        <f>L35*L35</f>
-        <v>324900</v>
-      </c>
-      <c r="T49" s="67">
-        <f>M35*M35</f>
-        <v>12159.4729</v>
-      </c>
-    </row>
-    <row r="50" ht="17" customHeight="1">
-      <c r="A50" s="62"/>
-      <c r="B50" t="s" s="70">
-        <v>44</v>
-      </c>
-      <c r="C50" s="71">
-        <f>C49+(C49*C49)/O11</f>
-        <v>2.085659568711575</v>
-      </c>
-      <c r="D50" t="s" s="70">
-        <v>44</v>
-      </c>
-      <c r="E50" s="71">
-        <f>E49+(E49*E49)/O11</f>
-        <v>3.121610784169308</v>
-      </c>
-      <c r="F50" t="s" s="70">
-        <v>44</v>
-      </c>
-      <c r="G50" s="71">
+      <c r="G50" s="65">
         <f>G49+(G49*G49)/O11</f>
         <v>5.224890885759959</v>
       </c>
-      <c r="H50" s="65"/>
-      <c r="I50" s="66">
-        <f>D36*E36</f>
+      <c r="H50" s="59"/>
+      <c r="I50" s="60">
+        <f t="shared" si="5"/>
         <v>261619.6</v>
       </c>
-      <c r="J50" s="66">
-        <f>(E36*E36)</f>
-        <v>124990.5316</v>
-      </c>
-      <c r="K50" s="66">
-        <f>H36*I36</f>
+      <c r="J50" s="60">
+        <f t="shared" si="6"/>
+        <v>124990.53160000002</v>
+      </c>
+      <c r="K50" s="60">
+        <f t="shared" si="7"/>
         <v>235812</v>
       </c>
-      <c r="L50" s="66">
-        <f>I36*I36</f>
+      <c r="L50" s="60">
+        <f t="shared" si="8"/>
         <v>75185.64</v>
       </c>
-      <c r="M50" s="66">
-        <f>L36*M36</f>
-        <v>119179.4</v>
-      </c>
-      <c r="N50" s="66">
-        <f>M36*M36</f>
-        <v>22758.7396</v>
-      </c>
-      <c r="O50" s="66">
-        <f>D36*D36</f>
+      <c r="M50" s="60">
+        <f t="shared" si="9"/>
+        <v>119179.40000000001</v>
+      </c>
+      <c r="N50" s="60">
+        <f t="shared" si="10"/>
+        <v>22758.739600000004</v>
+      </c>
+      <c r="O50" s="60">
+        <f t="shared" si="11"/>
         <v>547600</v>
       </c>
-      <c r="P50" s="66">
-        <f>E36*E36</f>
-        <v>124990.5316</v>
-      </c>
-      <c r="Q50" s="66">
-        <f>H36*H36</f>
+      <c r="P50" s="60">
+        <f t="shared" si="12"/>
+        <v>124990.53160000002</v>
+      </c>
+      <c r="Q50" s="60">
+        <f t="shared" si="13"/>
         <v>739600</v>
       </c>
-      <c r="R50" s="66">
-        <f>I36*I36</f>
+      <c r="R50" s="60">
+        <f t="shared" si="14"/>
         <v>75185.64</v>
       </c>
-      <c r="S50" s="66">
-        <f>L36*L36</f>
+      <c r="S50" s="60">
+        <f t="shared" si="15"/>
         <v>624100</v>
       </c>
-      <c r="T50" s="67">
-        <f>M36*M36</f>
-        <v>22758.7396</v>
-      </c>
-    </row>
-    <row r="51" ht="17" customHeight="1">
-      <c r="A51" s="62"/>
-      <c r="B51" t="s" s="70">
+      <c r="T50" s="61">
+        <f t="shared" si="16"/>
+        <v>22758.739600000004</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="57"/>
+      <c r="B51" s="64" t="s">
+        <v>44</v>
+      </c>
+      <c r="C51" s="65">
+        <f>P60</f>
+        <v>3.599041460087226E-3</v>
+      </c>
+      <c r="D51" s="64" t="s">
+        <v>44</v>
+      </c>
+      <c r="E51" s="65">
+        <f>R60</f>
+        <v>5.0265026449720389E-3</v>
+      </c>
+      <c r="F51" s="64" t="s">
+        <v>44</v>
+      </c>
+      <c r="G51" s="65">
+        <f>T60</f>
+        <v>7.5538598018458558E-3</v>
+      </c>
+      <c r="H51" s="59"/>
+      <c r="I51" s="60">
+        <f t="shared" si="5"/>
+        <v>344505</v>
+      </c>
+      <c r="J51" s="60">
+        <f t="shared" si="6"/>
+        <v>164268.09</v>
+      </c>
+      <c r="K51" s="60">
+        <f t="shared" si="7"/>
+        <v>184110</v>
+      </c>
+      <c r="L51" s="60">
+        <f t="shared" si="8"/>
+        <v>58685.0625</v>
+      </c>
+      <c r="M51" s="60">
+        <f t="shared" si="9"/>
+        <v>132326.9</v>
+      </c>
+      <c r="N51" s="60">
+        <f t="shared" si="10"/>
+        <v>25417.924900000002</v>
+      </c>
+      <c r="O51" s="60">
+        <f t="shared" si="11"/>
+        <v>722500</v>
+      </c>
+      <c r="P51" s="60">
+        <f t="shared" si="12"/>
+        <v>164268.09</v>
+      </c>
+      <c r="Q51" s="60">
+        <f t="shared" si="13"/>
+        <v>577600</v>
+      </c>
+      <c r="R51" s="60">
+        <f t="shared" si="14"/>
+        <v>58685.0625</v>
+      </c>
+      <c r="S51" s="60">
+        <f t="shared" si="15"/>
+        <v>688900</v>
+      </c>
+      <c r="T51" s="61">
+        <f t="shared" si="16"/>
+        <v>25417.924900000002</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="57"/>
+      <c r="B52" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="C51" s="71">
-        <f>P60</f>
-        <v>0.003599041460087226</v>
-      </c>
-      <c r="D51" t="s" s="70">
+      <c r="C52" s="65">
+        <f>SQRT(($O$10/2/MAX(D33:D44))*($O$10/2/MAX(D33:D44))+($P$10/2/MAX(E33:E44))*($P$10/2/MAX(E33:E44)))*C49</f>
+        <v>3.6346923213359918E-3</v>
+      </c>
+      <c r="D52" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="E51" s="71">
-        <f>R60</f>
-        <v>0.005026502644972039</v>
-      </c>
-      <c r="F51" t="s" s="70">
+      <c r="E52" s="65">
+        <f>SQRT(($O$10/2/MAX(H33:H44))*($O$10/2/MAX(H33:H44))+($P$10/2/MAX(I33:I44))*($P$10/2/MAX(I33:I44)))*E49</f>
+        <v>6.0484705729946155E-3</v>
+      </c>
+      <c r="F52" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="G51" s="71">
-        <f>T60</f>
-        <v>0.007553859801845856</v>
-      </c>
-      <c r="H51" s="65"/>
-      <c r="I51" s="66">
-        <f>D37*E37</f>
-        <v>344505</v>
-      </c>
-      <c r="J51" s="66">
-        <f>(E37*E37)</f>
-        <v>164268.09</v>
-      </c>
-      <c r="K51" s="66">
-        <f>H37*I37</f>
-        <v>184110</v>
-      </c>
-      <c r="L51" s="66">
-        <f>I37*I37</f>
-        <v>58685.0625</v>
-      </c>
-      <c r="M51" s="66">
-        <f>L37*M37</f>
-        <v>132326.9</v>
-      </c>
-      <c r="N51" s="66">
-        <f>M37*M37</f>
-        <v>25417.9249</v>
-      </c>
-      <c r="O51" s="66">
-        <f>D37*D37</f>
-        <v>722500</v>
-      </c>
-      <c r="P51" s="66">
-        <f>E37*E37</f>
-        <v>164268.09</v>
-      </c>
-      <c r="Q51" s="66">
-        <f>H37*H37</f>
-        <v>577600</v>
-      </c>
-      <c r="R51" s="66">
-        <f>I37*I37</f>
-        <v>58685.0625</v>
-      </c>
-      <c r="S51" s="66">
-        <f>L37*L37</f>
-        <v>688900</v>
-      </c>
-      <c r="T51" s="67">
-        <f>M37*M37</f>
-        <v>25417.9249</v>
-      </c>
-    </row>
-    <row r="52" ht="17" customHeight="1">
-      <c r="A52" s="62"/>
-      <c r="B52" t="s" s="70">
+      <c r="G52" s="65">
+        <f>SQRT(($O$10/2/MAX(L33:L44))*($O$10/2/MAX(L33:L44))+($P$10/2/MAX(M33:M44))*($P$10/2/MAX(M33:M44)))*G49</f>
+        <v>1.400519014846697E-2</v>
+      </c>
+      <c r="H52" s="59"/>
+      <c r="I52" s="60">
+        <f t="shared" si="5"/>
+        <v>452233.4</v>
+      </c>
+      <c r="J52" s="60">
+        <f t="shared" si="6"/>
+        <v>217361.08840000004</v>
+      </c>
+      <c r="K52" s="60">
+        <f t="shared" si="7"/>
+        <v>309062.59999999998</v>
+      </c>
+      <c r="L52" s="60">
+        <f t="shared" si="8"/>
+        <v>99458.236900000004</v>
+      </c>
+      <c r="M52" s="60">
+        <f t="shared" si="9"/>
+        <v>162021.20000000001</v>
+      </c>
+      <c r="N52" s="60">
+        <f t="shared" si="10"/>
+        <v>31014.732100000005</v>
+      </c>
+      <c r="O52" s="60">
+        <f t="shared" si="11"/>
+        <v>940900</v>
+      </c>
+      <c r="P52" s="60">
+        <f t="shared" si="12"/>
+        <v>217361.08840000004</v>
+      </c>
+      <c r="Q52" s="60">
+        <f t="shared" si="13"/>
+        <v>960400</v>
+      </c>
+      <c r="R52" s="60">
+        <f t="shared" si="14"/>
+        <v>99458.236900000004</v>
+      </c>
+      <c r="S52" s="60">
+        <f t="shared" si="15"/>
+        <v>846400</v>
+      </c>
+      <c r="T52" s="61">
+        <f t="shared" si="16"/>
+        <v>31014.732100000005</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="57"/>
+      <c r="B53" s="66" t="s">
         <v>46</v>
       </c>
-      <c r="C52" s="71">
-        <f>SQRT(($O$10/2/MAX(D33:D44))*($O$10/2/MAX(D33:D44))+($P$10/2/MAX(E33:E44))*($P$10/2/MAX(E33:E44)))*C49</f>
-        <v>0.003634692321335992</v>
-      </c>
-      <c r="D52" t="s" s="70">
+      <c r="C53" s="67">
+        <f>SQRT(C51*C51+C52*C52)</f>
+        <v>5.1150843299212195E-3</v>
+      </c>
+      <c r="D53" s="66" t="s">
         <v>46</v>
       </c>
-      <c r="E52" s="71">
-        <f>SQRT(($O$10/2/MAX(H33:H44))*($O$10/2/MAX(H33:H44))+($P$10/2/MAX(I33:I44))*($P$10/2/MAX(I33:I44)))*E49</f>
-        <v>0.006048470572994616</v>
-      </c>
-      <c r="F52" t="s" s="70">
+      <c r="E53" s="67">
+        <f>SQRT(E51*E51+E52*E52)</f>
+        <v>7.8644596198526387E-3</v>
+      </c>
+      <c r="F53" s="66" t="s">
         <v>46</v>
       </c>
-      <c r="G52" s="71">
-        <f>SQRT(($O$10/2/MAX(L33:L44))*($O$10/2/MAX(L33:L44))+($P$10/2/MAX(M33:M44))*($P$10/2/MAX(M33:M44)))*G49</f>
-        <v>0.01400519014846697</v>
-      </c>
-      <c r="H52" s="65"/>
-      <c r="I52" s="66">
-        <f>D38*E38</f>
-        <v>452233.4</v>
-      </c>
-      <c r="J52" s="66">
-        <f>(E38*E38)</f>
-        <v>217361.0884</v>
-      </c>
-      <c r="K52" s="66">
-        <f>H38*I38</f>
-        <v>309062.6</v>
-      </c>
-      <c r="L52" s="66">
-        <f>I38*I38</f>
-        <v>99458.2369</v>
-      </c>
-      <c r="M52" s="66">
-        <f>L38*M38</f>
-        <v>162021.2</v>
-      </c>
-      <c r="N52" s="66">
-        <f>M38*M38</f>
-        <v>31014.7321</v>
-      </c>
-      <c r="O52" s="66">
-        <f>D38*D38</f>
-        <v>940900</v>
-      </c>
-      <c r="P52" s="66">
-        <f>E38*E38</f>
-        <v>217361.0884</v>
-      </c>
-      <c r="Q52" s="66">
-        <f>H38*H38</f>
-        <v>960400</v>
-      </c>
-      <c r="R52" s="66">
-        <f>I38*I38</f>
-        <v>99458.2369</v>
-      </c>
-      <c r="S52" s="66">
-        <f>L38*L38</f>
-        <v>846400</v>
-      </c>
-      <c r="T52" s="67">
-        <f>M38*M38</f>
-        <v>31014.7321</v>
-      </c>
-    </row>
-    <row r="53" ht="17" customHeight="1">
-      <c r="A53" s="62"/>
-      <c r="B53" t="s" s="72">
+      <c r="G53" s="67">
+        <f>SQRT(G51*G51+G52*G52)</f>
+        <v>1.5912452639384633E-2</v>
+      </c>
+      <c r="H53" s="59"/>
+      <c r="I53" s="60">
+        <f t="shared" si="5"/>
+        <v>286332.2</v>
+      </c>
+      <c r="J53" s="60">
+        <f t="shared" si="6"/>
+        <v>138279.8596</v>
+      </c>
+      <c r="K53" s="60">
+        <f t="shared" si="7"/>
+        <v>199767.30000000002</v>
+      </c>
+      <c r="L53" s="60">
+        <f t="shared" si="8"/>
+        <v>63943.236900000004</v>
+      </c>
+      <c r="M53" s="60">
+        <f t="shared" si="9"/>
+        <v>158613</v>
+      </c>
+      <c r="N53" s="60">
+        <f t="shared" si="10"/>
+        <v>30380.490000000005</v>
+      </c>
+      <c r="O53" s="60">
+        <f t="shared" si="11"/>
+        <v>592900</v>
+      </c>
+      <c r="P53" s="60">
+        <f t="shared" si="12"/>
+        <v>138279.8596</v>
+      </c>
+      <c r="Q53" s="60">
+        <f t="shared" si="13"/>
+        <v>624100</v>
+      </c>
+      <c r="R53" s="60">
+        <f t="shared" si="14"/>
+        <v>63943.236900000004</v>
+      </c>
+      <c r="S53" s="60">
+        <f t="shared" si="15"/>
+        <v>828100</v>
+      </c>
+      <c r="T53" s="61">
+        <f t="shared" si="16"/>
+        <v>30380.490000000005</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="68"/>
+      <c r="B54" s="69"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="71"/>
+      <c r="G54" s="72"/>
+      <c r="H54" s="73"/>
+      <c r="I54" s="60">
+        <f t="shared" si="5"/>
+        <v>221890.8</v>
+      </c>
+      <c r="J54" s="60">
+        <f t="shared" si="6"/>
+        <v>106478.21610000001</v>
+      </c>
+      <c r="K54" s="60">
+        <f t="shared" si="7"/>
+        <v>119755.2</v>
+      </c>
+      <c r="L54" s="60">
+        <f t="shared" si="8"/>
+        <v>38541.542399999998</v>
+      </c>
+      <c r="M54" s="60">
+        <f t="shared" si="9"/>
+        <v>115861.2</v>
+      </c>
+      <c r="N54" s="60">
+        <f t="shared" si="10"/>
+        <v>22064.131599999997</v>
+      </c>
+      <c r="O54" s="60">
+        <f t="shared" si="11"/>
+        <v>462400</v>
+      </c>
+      <c r="P54" s="60">
+        <f t="shared" si="12"/>
+        <v>106478.21610000001</v>
+      </c>
+      <c r="Q54" s="60">
+        <f t="shared" si="13"/>
+        <v>372100</v>
+      </c>
+      <c r="R54" s="60">
+        <f t="shared" si="14"/>
+        <v>38541.542399999998</v>
+      </c>
+      <c r="S54" s="60">
+        <f t="shared" si="15"/>
+        <v>608400</v>
+      </c>
+      <c r="T54" s="61">
+        <f t="shared" si="16"/>
+        <v>22064.131599999997</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="57"/>
+      <c r="B55" s="74" t="s">
         <v>47</v>
       </c>
-      <c r="C53" s="73">
-        <f>SQRT(C51*C51+C52*C52)</f>
-        <v>0.005115084329921219</v>
-      </c>
-      <c r="D53" t="s" s="72">
+      <c r="C55" s="75">
+        <v>20</v>
+      </c>
+      <c r="D55" s="76">
+        <v>30</v>
+      </c>
+      <c r="E55" s="77">
+        <v>50</v>
+      </c>
+      <c r="F55" s="59"/>
+      <c r="G55" s="73"/>
+      <c r="H55" s="73"/>
+      <c r="I55" s="60">
+        <f t="shared" si="5"/>
+        <v>154641</v>
+      </c>
+      <c r="J55" s="60">
+        <f t="shared" si="6"/>
+        <v>73603.69</v>
+      </c>
+      <c r="K55" s="60">
+        <f t="shared" si="7"/>
+        <v>97784.5</v>
+      </c>
+      <c r="L55" s="60">
+        <f t="shared" si="8"/>
+        <v>31609.284099999997</v>
+      </c>
+      <c r="M55" s="60">
+        <f t="shared" si="9"/>
+        <v>78489.600000000006</v>
+      </c>
+      <c r="N55" s="60">
+        <f t="shared" si="10"/>
+        <v>15040.569600000001</v>
+      </c>
+      <c r="O55" s="60">
+        <f t="shared" si="11"/>
+        <v>324900</v>
+      </c>
+      <c r="P55" s="60">
+        <f t="shared" si="12"/>
+        <v>73603.69</v>
+      </c>
+      <c r="Q55" s="60">
+        <f t="shared" si="13"/>
+        <v>302500</v>
+      </c>
+      <c r="R55" s="60">
+        <f t="shared" si="14"/>
+        <v>31609.284099999997</v>
+      </c>
+      <c r="S55" s="60">
+        <f t="shared" si="15"/>
+        <v>409600</v>
+      </c>
+      <c r="T55" s="61">
+        <f t="shared" si="16"/>
+        <v>15040.569600000001</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="57"/>
+      <c r="B56" s="62" t="s">
+        <v>48</v>
+      </c>
+      <c r="C56" s="39">
+        <f>C49</f>
+        <v>2.0852247524847378</v>
+      </c>
+      <c r="D56" s="41">
+        <f>E49</f>
+        <v>3.1206369466740131</v>
+      </c>
+      <c r="E56" s="42">
+        <f>G49</f>
+        <v>5.2221637862988661</v>
+      </c>
+      <c r="F56" s="59"/>
+      <c r="G56" s="73"/>
+      <c r="H56" s="73"/>
+      <c r="I56" s="60">
+        <f t="shared" si="5"/>
+        <v>120775</v>
+      </c>
+      <c r="J56" s="60">
+        <f t="shared" si="6"/>
+        <v>58346.402500000004</v>
+      </c>
+      <c r="K56" s="60">
+        <f t="shared" si="7"/>
+        <v>71101.600000000006</v>
+      </c>
+      <c r="L56" s="60">
+        <f t="shared" si="8"/>
+        <v>22885.6384</v>
+      </c>
+      <c r="M56" s="60">
+        <f t="shared" si="9"/>
+        <v>48265</v>
+      </c>
+      <c r="N56" s="60">
+        <f t="shared" si="10"/>
+        <v>9318.0409</v>
+      </c>
+      <c r="O56" s="60">
+        <f t="shared" si="11"/>
+        <v>250000</v>
+      </c>
+      <c r="P56" s="60">
+        <f t="shared" si="12"/>
+        <v>58346.402500000004</v>
+      </c>
+      <c r="Q56" s="60">
+        <f t="shared" si="13"/>
+        <v>220900</v>
+      </c>
+      <c r="R56" s="60">
+        <f t="shared" si="14"/>
+        <v>22885.6384</v>
+      </c>
+      <c r="S56" s="60">
+        <f t="shared" si="15"/>
+        <v>250000</v>
+      </c>
+      <c r="T56" s="61">
+        <f t="shared" si="16"/>
+        <v>9318.0409</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="57"/>
+      <c r="B57" s="66" t="s">
+        <v>49</v>
+      </c>
+      <c r="C57" s="47">
+        <f>C53</f>
+        <v>5.1150843299212195E-3</v>
+      </c>
+      <c r="D57" s="49">
+        <f>E53</f>
+        <v>7.8644596198526387E-3</v>
+      </c>
+      <c r="E57" s="50">
+        <f>G53</f>
+        <v>1.5912452639384633E-2</v>
+      </c>
+      <c r="F57" s="59"/>
+      <c r="G57" s="73"/>
+      <c r="H57" s="73"/>
+      <c r="I57" s="60">
+        <f t="shared" si="5"/>
+        <v>84487.2</v>
+      </c>
+      <c r="J57" s="60">
+        <f t="shared" si="6"/>
+        <v>40465.345600000001</v>
+      </c>
+      <c r="K57" s="60">
+        <f t="shared" si="7"/>
+        <v>43630.400000000001</v>
+      </c>
+      <c r="L57" s="60">
+        <f t="shared" si="8"/>
+        <v>13905.126400000001</v>
+      </c>
+      <c r="M57" s="60">
+        <f t="shared" si="9"/>
+        <v>29152.5</v>
+      </c>
+      <c r="N57" s="60">
+        <f t="shared" si="10"/>
+        <v>5587.5625</v>
+      </c>
+      <c r="O57" s="60">
+        <f t="shared" si="11"/>
+        <v>176400</v>
+      </c>
+      <c r="P57" s="60">
+        <f t="shared" si="12"/>
+        <v>40465.345600000001</v>
+      </c>
+      <c r="Q57" s="60">
+        <f t="shared" si="13"/>
+        <v>136900</v>
+      </c>
+      <c r="R57" s="60">
+        <f t="shared" si="14"/>
+        <v>13905.126400000001</v>
+      </c>
+      <c r="S57" s="60">
+        <f t="shared" si="15"/>
+        <v>152100</v>
+      </c>
+      <c r="T57" s="61">
+        <f t="shared" si="16"/>
+        <v>5587.5625</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="68"/>
+      <c r="B58" s="78"/>
+      <c r="C58" s="78"/>
+      <c r="D58" s="78"/>
+      <c r="E58" s="79"/>
+      <c r="F58" s="73"/>
+      <c r="G58" s="73"/>
+      <c r="H58" s="73"/>
+      <c r="I58" s="60">
+        <f t="shared" si="5"/>
+        <v>53189.4</v>
+      </c>
+      <c r="J58" s="60">
+        <f t="shared" si="6"/>
+        <v>25978.992400000003</v>
+      </c>
+      <c r="K58" s="60">
+        <f t="shared" si="7"/>
+        <v>20062.5</v>
+      </c>
+      <c r="L58" s="60">
+        <f t="shared" si="8"/>
+        <v>6440.0625</v>
+      </c>
+      <c r="M58" s="60">
+        <f t="shared" si="9"/>
+        <v>13608</v>
+      </c>
+      <c r="N58" s="60">
+        <f t="shared" si="10"/>
+        <v>2540.16</v>
+      </c>
+      <c r="O58" s="60">
+        <f t="shared" si="11"/>
+        <v>108900</v>
+      </c>
+      <c r="P58" s="60">
+        <f t="shared" si="12"/>
+        <v>25978.992400000003</v>
+      </c>
+      <c r="Q58" s="60">
+        <f t="shared" si="13"/>
+        <v>62500</v>
+      </c>
+      <c r="R58" s="60">
+        <f t="shared" si="14"/>
+        <v>6440.0625</v>
+      </c>
+      <c r="S58" s="60">
+        <f t="shared" si="15"/>
+        <v>72900</v>
+      </c>
+      <c r="T58" s="61">
+        <f t="shared" si="16"/>
+        <v>2540.16</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="57"/>
+      <c r="B59" s="74" t="s">
         <v>47</v>
       </c>
-      <c r="E53" s="73">
-        <f>SQRT(E51*E51+E52*E52)</f>
-        <v>0.007864459619852639</v>
-      </c>
-      <c r="F53" t="s" s="72">
-        <v>47</v>
-      </c>
-      <c r="G53" s="73">
-        <f>SQRT(G51*G51+G52*G52)</f>
-        <v>0.01591245263938463</v>
-      </c>
-      <c r="H53" s="65"/>
-      <c r="I53" s="66">
-        <f>D39*E39</f>
-        <v>286332.2</v>
-      </c>
-      <c r="J53" s="66">
-        <f>(E39*E39)</f>
-        <v>138279.8596</v>
-      </c>
-      <c r="K53" s="66">
-        <f>H39*I39</f>
-        <v>199767.3</v>
-      </c>
-      <c r="L53" s="66">
-        <f>I39*I39</f>
-        <v>63943.2369</v>
-      </c>
-      <c r="M53" s="66">
-        <f>L39*M39</f>
-        <v>158613</v>
-      </c>
-      <c r="N53" s="66">
-        <f>M39*M39</f>
-        <v>30380.490000000005</v>
-      </c>
-      <c r="O53" s="66">
-        <f>D39*D39</f>
-        <v>592900</v>
-      </c>
-      <c r="P53" s="66">
-        <f>E39*E39</f>
-        <v>138279.8596</v>
-      </c>
-      <c r="Q53" s="66">
-        <f>H39*H39</f>
-        <v>624100</v>
-      </c>
-      <c r="R53" s="66">
-        <f>I39*I39</f>
-        <v>63943.2369</v>
-      </c>
-      <c r="S53" s="66">
-        <f>L39*L39</f>
-        <v>828100</v>
-      </c>
-      <c r="T53" s="67">
-        <f>M39*M39</f>
-        <v>30380.490000000005</v>
-      </c>
-    </row>
-    <row r="54" ht="17" customHeight="1">
-      <c r="A54" s="74"/>
-      <c r="B54" s="75"/>
-      <c r="C54" s="76"/>
-      <c r="D54" s="76"/>
-      <c r="E54" s="76"/>
-      <c r="F54" s="77"/>
-      <c r="G54" s="78"/>
-      <c r="H54" s="79"/>
-      <c r="I54" s="66">
-        <f>D40*E40</f>
-        <v>221890.8</v>
-      </c>
-      <c r="J54" s="66">
-        <f>(E40*E40)</f>
-        <v>106478.2161</v>
-      </c>
-      <c r="K54" s="66">
-        <f>H40*I40</f>
-        <v>119755.2</v>
-      </c>
-      <c r="L54" s="66">
-        <f>I40*I40</f>
-        <v>38541.5424</v>
-      </c>
-      <c r="M54" s="66">
-        <f>L40*M40</f>
-        <v>115861.2</v>
-      </c>
-      <c r="N54" s="66">
-        <f>M40*M40</f>
-        <v>22064.1316</v>
-      </c>
-      <c r="O54" s="66">
-        <f>D40*D40</f>
-        <v>462400</v>
-      </c>
-      <c r="P54" s="66">
-        <f>E40*E40</f>
-        <v>106478.2161</v>
-      </c>
-      <c r="Q54" s="66">
-        <f>H40*H40</f>
-        <v>372100</v>
-      </c>
-      <c r="R54" s="66">
-        <f>I40*I40</f>
-        <v>38541.5424</v>
-      </c>
-      <c r="S54" s="66">
-        <f>L40*L40</f>
-        <v>608400</v>
-      </c>
-      <c r="T54" s="67">
-        <f>M40*M40</f>
-        <v>22064.1316</v>
-      </c>
-    </row>
-    <row r="55" ht="17" customHeight="1">
-      <c r="A55" s="62"/>
-      <c r="B55" t="s" s="80">
-        <v>48</v>
-      </c>
-      <c r="C55" s="81">
+      <c r="C59" s="58" t="s">
+        <v>50</v>
+      </c>
+      <c r="D59" s="80" t="s">
+        <v>51</v>
+      </c>
+      <c r="E59" s="59"/>
+      <c r="F59" s="73"/>
+      <c r="G59" s="73"/>
+      <c r="H59" s="73"/>
+      <c r="I59" s="60">
+        <f t="shared" ref="I59:T59" si="17">AVERAGE(I47:I58)</f>
+        <v>201749.61666666667</v>
+      </c>
+      <c r="J59" s="60">
+        <f t="shared" si="17"/>
+        <v>96751.976700000014</v>
+      </c>
+      <c r="K59" s="60">
+        <f t="shared" si="17"/>
+        <v>126847.825</v>
+      </c>
+      <c r="L59" s="60">
+        <f t="shared" si="17"/>
+        <v>40648.055883333334</v>
+      </c>
+      <c r="M59" s="60">
+        <f t="shared" si="17"/>
+        <v>82944.05833333332</v>
+      </c>
+      <c r="N59" s="60">
+        <f t="shared" si="17"/>
+        <v>15883.082516666667</v>
+      </c>
+      <c r="O59" s="60">
+        <f t="shared" si="17"/>
+        <v>420708.33333333331</v>
+      </c>
+      <c r="P59" s="60">
+        <f t="shared" si="17"/>
+        <v>96751.976700000014</v>
+      </c>
+      <c r="Q59" s="60">
+        <f t="shared" si="17"/>
+        <v>395858.33333333331</v>
+      </c>
+      <c r="R59" s="60">
+        <f t="shared" si="17"/>
+        <v>40648.055883333334</v>
+      </c>
+      <c r="S59" s="60">
+        <f t="shared" si="17"/>
+        <v>433158.33333333331</v>
+      </c>
+      <c r="T59" s="61">
+        <f t="shared" si="17"/>
+        <v>15883.082516666667</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="57"/>
+      <c r="B60" s="63">
         <v>20</v>
       </c>
-      <c r="D55" s="82">
+      <c r="C60" s="39">
+        <f>(C50/B60)*(PI()*$G$19*$G$19/4)*100</f>
+        <v>0.97485831001868173</v>
+      </c>
+      <c r="D60" s="42">
+        <f>SQRT((C57/C56)*(C57/C56)+(2*$D$22/$G$19)*(2*$D$22/$G$19)+(0.1/B60)*(0.1/B60))*100</f>
+        <v>6.1192506411839132</v>
+      </c>
+      <c r="E60" s="59"/>
+      <c r="F60" s="73"/>
+      <c r="G60" s="73"/>
+      <c r="H60" s="73"/>
+      <c r="I60" s="81"/>
+      <c r="J60" s="60">
+        <f>I59/J59</f>
+        <v>2.0852247524847378</v>
+      </c>
+      <c r="K60" s="81"/>
+      <c r="L60" s="60">
+        <f>K59/L59</f>
+        <v>3.1206369466740131</v>
+      </c>
+      <c r="M60" s="81"/>
+      <c r="N60" s="60">
+        <f>M59/N59</f>
+        <v>5.2221637862988661</v>
+      </c>
+      <c r="O60" s="60"/>
+      <c r="P60" s="60">
+        <f>1/SQRT(12)*SQRT(O59/P59-J60*J60)</f>
+        <v>3.599041460087226E-3</v>
+      </c>
+      <c r="Q60" s="82"/>
+      <c r="R60" s="82">
+        <f>1/SQRT(12)*SQRT(Q59/R59-L60*L60)</f>
+        <v>5.0265026449720389E-3</v>
+      </c>
+      <c r="S60" s="82"/>
+      <c r="T60" s="83">
+        <f>1/SQRT(12)*SQRT(S59/T59-N60*N60)</f>
+        <v>7.5538598018458558E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="57"/>
+      <c r="B61" s="65">
         <v>30</v>
       </c>
-      <c r="E55" s="83">
+      <c r="C61" s="44">
+        <f>(E50/B61)*(PI()*$G$19*$G$19/4)*100</f>
+        <v>0.97271490171693054</v>
+      </c>
+      <c r="D61" s="46">
+        <f>SQRT((C57/C56)*(C57/C56)+(2*$D$22/$G$19)*(2*$D$22/$G$19)+(0.1/B61)*(0.1/B61))*100</f>
+        <v>6.1078915773563667</v>
+      </c>
+      <c r="E61" s="59"/>
+      <c r="F61" s="84"/>
+      <c r="G61" s="84"/>
+      <c r="H61" s="84"/>
+      <c r="I61" s="84"/>
+      <c r="J61" s="73"/>
+      <c r="K61" s="73"/>
+      <c r="L61" s="73"/>
+      <c r="M61" s="73"/>
+      <c r="N61" s="73"/>
+      <c r="O61" s="73"/>
+      <c r="P61" s="73"/>
+      <c r="Q61" s="55"/>
+      <c r="R61" s="55"/>
+      <c r="S61" s="55"/>
+      <c r="T61" s="56"/>
+    </row>
+    <row r="62" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="85"/>
+      <c r="B62" s="67">
         <v>50</v>
       </c>
-      <c r="F55" s="65"/>
-      <c r="G55" s="79"/>
-      <c r="H55" s="79"/>
-      <c r="I55" s="66">
-        <f>D41*E41</f>
-        <v>154641</v>
-      </c>
-      <c r="J55" s="66">
-        <f>(E41*E41)</f>
-        <v>73603.69</v>
-      </c>
-      <c r="K55" s="66">
-        <f>H41*I41</f>
-        <v>97784.5</v>
-      </c>
-      <c r="L55" s="66">
-        <f>I41*I41</f>
-        <v>31609.2841</v>
-      </c>
-      <c r="M55" s="66">
-        <f>L41*M41</f>
-        <v>78489.600000000006</v>
-      </c>
-      <c r="N55" s="66">
-        <f>M41*M41</f>
-        <v>15040.5696</v>
-      </c>
-      <c r="O55" s="66">
-        <f>D41*D41</f>
-        <v>324900</v>
-      </c>
-      <c r="P55" s="66">
-        <f>E41*E41</f>
-        <v>73603.69</v>
-      </c>
-      <c r="Q55" s="66">
-        <f>H41*H41</f>
-        <v>302500</v>
-      </c>
-      <c r="R55" s="66">
-        <f>I41*I41</f>
-        <v>31609.2841</v>
-      </c>
-      <c r="S55" s="66">
-        <f>L41*L41</f>
-        <v>409600</v>
-      </c>
-      <c r="T55" s="67">
-        <f>M41*M41</f>
-        <v>15040.5696</v>
-      </c>
-    </row>
-    <row r="56" ht="17" customHeight="1">
-      <c r="A56" s="62"/>
-      <c r="B56" t="s" s="68">
-        <v>49</v>
-      </c>
-      <c r="C56" s="43">
-        <f>C49</f>
-        <v>2.085224752484738</v>
-      </c>
-      <c r="D56" s="45">
-        <f>E49</f>
-        <v>3.120636946674013</v>
-      </c>
-      <c r="E56" s="46">
-        <f>G49</f>
-        <v>5.222163786298866</v>
-      </c>
-      <c r="F56" s="65"/>
-      <c r="G56" s="79"/>
-      <c r="H56" s="79"/>
-      <c r="I56" s="66">
-        <f>D42*E42</f>
-        <v>120775</v>
-      </c>
-      <c r="J56" s="66">
-        <f>(E42*E42)</f>
-        <v>58346.4025</v>
-      </c>
-      <c r="K56" s="66">
-        <f>H42*I42</f>
-        <v>71101.600000000006</v>
-      </c>
-      <c r="L56" s="66">
-        <f>I42*I42</f>
-        <v>22885.6384</v>
-      </c>
-      <c r="M56" s="66">
-        <f>L42*M42</f>
-        <v>48265</v>
-      </c>
-      <c r="N56" s="66">
-        <f>M42*M42</f>
-        <v>9318.0409</v>
-      </c>
-      <c r="O56" s="66">
-        <f>D42*D42</f>
-        <v>250000</v>
-      </c>
-      <c r="P56" s="66">
-        <f>E42*E42</f>
-        <v>58346.4025</v>
-      </c>
-      <c r="Q56" s="66">
-        <f>H42*H42</f>
-        <v>220900</v>
-      </c>
-      <c r="R56" s="66">
-        <f>I42*I42</f>
-        <v>22885.6384</v>
-      </c>
-      <c r="S56" s="66">
-        <f>L42*L42</f>
-        <v>250000</v>
-      </c>
-      <c r="T56" s="67">
-        <f>M42*M42</f>
-        <v>9318.0409</v>
-      </c>
-    </row>
-    <row r="57" ht="17" customHeight="1">
-      <c r="A57" s="62"/>
-      <c r="B57" t="s" s="72">
-        <v>50</v>
-      </c>
-      <c r="C57" s="51">
-        <f>C53</f>
-        <v>0.005115084329921219</v>
-      </c>
-      <c r="D57" s="53">
-        <f>E53</f>
-        <v>0.007864459619852639</v>
-      </c>
-      <c r="E57" s="54">
-        <f>G53</f>
-        <v>0.01591245263938463</v>
-      </c>
-      <c r="F57" s="65"/>
-      <c r="G57" s="79"/>
-      <c r="H57" s="79"/>
-      <c r="I57" s="66">
-        <f>D43*E43</f>
-        <v>84487.2</v>
-      </c>
-      <c r="J57" s="66">
-        <f>(E43*E43)</f>
-        <v>40465.3456</v>
-      </c>
-      <c r="K57" s="66">
-        <f>H43*I43</f>
-        <v>43630.4</v>
-      </c>
-      <c r="L57" s="66">
-        <f>I43*I43</f>
-        <v>13905.1264</v>
-      </c>
-      <c r="M57" s="66">
-        <f>L43*M43</f>
-        <v>29152.5</v>
-      </c>
-      <c r="N57" s="66">
-        <f>M43*M43</f>
-        <v>5587.5625</v>
-      </c>
-      <c r="O57" s="66">
-        <f>D43*D43</f>
-        <v>176400</v>
-      </c>
-      <c r="P57" s="66">
-        <f>E43*E43</f>
-        <v>40465.3456</v>
-      </c>
-      <c r="Q57" s="66">
-        <f>H43*H43</f>
-        <v>136900</v>
-      </c>
-      <c r="R57" s="66">
-        <f>I43*I43</f>
-        <v>13905.1264</v>
-      </c>
-      <c r="S57" s="66">
-        <f>L43*L43</f>
-        <v>152100</v>
-      </c>
-      <c r="T57" s="67">
-        <f>M43*M43</f>
-        <v>5587.5625</v>
-      </c>
-    </row>
-    <row r="58" ht="17" customHeight="1">
-      <c r="A58" s="74"/>
-      <c r="B58" s="84"/>
-      <c r="C58" s="84"/>
-      <c r="D58" s="84"/>
-      <c r="E58" s="85"/>
-      <c r="F58" s="79"/>
-      <c r="G58" s="79"/>
-      <c r="H58" s="79"/>
-      <c r="I58" s="66">
-        <f>D44*E44</f>
-        <v>53189.4</v>
-      </c>
-      <c r="J58" s="66">
-        <f>(E44*E44)</f>
-        <v>25978.9924</v>
-      </c>
-      <c r="K58" s="66">
-        <f>H44*I44</f>
-        <v>20062.5</v>
-      </c>
-      <c r="L58" s="66">
-        <f>I44*I44</f>
-        <v>6440.0625</v>
-      </c>
-      <c r="M58" s="66">
-        <f>L44*M44</f>
-        <v>13608</v>
-      </c>
-      <c r="N58" s="66">
-        <f>M44*M44</f>
-        <v>2540.16</v>
-      </c>
-      <c r="O58" s="66">
-        <f>D44*D44</f>
-        <v>108900</v>
-      </c>
-      <c r="P58" s="66">
-        <f>E44*E44</f>
-        <v>25978.9924</v>
-      </c>
-      <c r="Q58" s="66">
-        <f>H44*H44</f>
-        <v>62500</v>
-      </c>
-      <c r="R58" s="66">
-        <f>I44*I44</f>
-        <v>6440.0625</v>
-      </c>
-      <c r="S58" s="66">
-        <f>L44*L44</f>
-        <v>72900</v>
-      </c>
-      <c r="T58" s="67">
-        <f>M44*M44</f>
-        <v>2540.16</v>
-      </c>
-    </row>
-    <row r="59" ht="17" customHeight="1">
-      <c r="A59" s="62"/>
-      <c r="B59" t="s" s="80">
-        <v>48</v>
-      </c>
-      <c r="C59" t="s" s="63">
-        <v>51</v>
-      </c>
-      <c r="D59" t="s" s="86">
+      <c r="C62" s="47">
+        <f>(G50/B62)*(PI()*$G$19*$G$19/4)*100</f>
+        <v>0.97686667092473112</v>
+      </c>
+      <c r="D62" s="50">
+        <f>SQRT((C57/C56)*(C57/C56)+(2*$D$22/$G$19)*(2*$D$22/$G$19)+(0.1/B62)*(0.1/B62))*100</f>
+        <v>6.1020675520375667</v>
+      </c>
+      <c r="E62" s="86"/>
+      <c r="F62" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="E59" s="65"/>
-      <c r="F59" s="79"/>
-      <c r="G59" s="79"/>
-      <c r="H59" s="79"/>
-      <c r="I59" s="66">
-        <f>AVERAGE(I47:I58)</f>
-        <v>201749.6166666667</v>
-      </c>
-      <c r="J59" s="66">
-        <f>AVERAGE(J47:J58)</f>
-        <v>96751.976700000014</v>
-      </c>
-      <c r="K59" s="66">
-        <f>AVERAGE(K47:K58)</f>
-        <v>126847.825</v>
-      </c>
-      <c r="L59" s="66">
-        <f>AVERAGE(L47:L58)</f>
-        <v>40648.055883333334</v>
-      </c>
-      <c r="M59" s="66">
-        <f>AVERAGE(M47:M58)</f>
-        <v>82944.058333333320</v>
-      </c>
-      <c r="N59" s="66">
-        <f>AVERAGE(N47:N58)</f>
-        <v>15883.082516666667</v>
-      </c>
-      <c r="O59" s="66">
-        <f>AVERAGE(O47:O58)</f>
-        <v>420708.3333333333</v>
-      </c>
-      <c r="P59" s="66">
-        <f>AVERAGE(P47:P58)</f>
-        <v>96751.976700000014</v>
-      </c>
-      <c r="Q59" s="66">
-        <f>AVERAGE(Q47:Q58)</f>
-        <v>395858.3333333333</v>
-      </c>
-      <c r="R59" s="66">
-        <f>AVERAGE(R47:R58)</f>
-        <v>40648.055883333334</v>
-      </c>
-      <c r="S59" s="66">
-        <f>AVERAGE(S47:S58)</f>
-        <v>433158.3333333333</v>
-      </c>
-      <c r="T59" s="67">
-        <f>AVERAGE(T47:T58)</f>
-        <v>15883.082516666667</v>
-      </c>
-    </row>
-    <row r="60" ht="17" customHeight="1">
-      <c r="A60" s="62"/>
-      <c r="B60" s="69">
-        <v>20</v>
-      </c>
-      <c r="C60" s="43">
-        <f>(C50/B60)*(PI()*$G$19*$G$19/4)*100</f>
-        <v>0.9748583100186817</v>
-      </c>
-      <c r="D60" s="46">
-        <f>SQRT((C57/C56)*(C57/C56)+(2*$D$22/$G$19)*(2*$D$22/$G$19)+(0.1/B60)*(0.1/B60))*100</f>
-        <v>6.119250641183913</v>
-      </c>
-      <c r="E60" s="65"/>
-      <c r="F60" s="79"/>
-      <c r="G60" s="79"/>
-      <c r="H60" s="79"/>
-      <c r="I60" s="87"/>
-      <c r="J60" s="66">
-        <f>I59/J59</f>
-        <v>2.085224752484738</v>
-      </c>
-      <c r="K60" s="87"/>
-      <c r="L60" s="66">
-        <f>K59/L59</f>
-        <v>3.120636946674013</v>
-      </c>
-      <c r="M60" s="87"/>
-      <c r="N60" s="66">
-        <f>M59/N59</f>
-        <v>5.222163786298866</v>
-      </c>
-      <c r="O60" s="66"/>
-      <c r="P60" s="66">
-        <f>1/SQRT(12)*SQRT(O59/P59-J60*J60)</f>
-        <v>0.003599041460087226</v>
-      </c>
-      <c r="Q60" s="88"/>
-      <c r="R60" s="88">
-        <f>1/SQRT(12)*SQRT(Q59/R59-L60*L60)</f>
-        <v>0.005026502644972039</v>
-      </c>
-      <c r="S60" s="88"/>
-      <c r="T60" s="89">
-        <f>1/SQRT(12)*SQRT(S59/T59-N60*N60)</f>
-        <v>0.007553859801845856</v>
-      </c>
-    </row>
-    <row r="61" ht="17" customHeight="1">
-      <c r="A61" s="62"/>
-      <c r="B61" s="71">
-        <v>30</v>
-      </c>
-      <c r="C61" s="48">
-        <f>(E50/B61)*(PI()*$G$19*$G$19/4)*100</f>
-        <v>0.9727149017169305</v>
-      </c>
-      <c r="D61" s="50">
-        <f>SQRT((C57/C56)*(C57/C56)+(2*$D$22/$G$19)*(2*$D$22/$G$19)+(0.1/B61)*(0.1/B61))*100</f>
-        <v>6.107891577356367</v>
-      </c>
-      <c r="E61" s="65"/>
-      <c r="F61" s="90"/>
-      <c r="G61" s="90"/>
-      <c r="H61" s="90"/>
-      <c r="I61" s="90"/>
-      <c r="J61" s="79"/>
-      <c r="K61" s="79"/>
-      <c r="L61" s="79"/>
-      <c r="M61" s="79"/>
-      <c r="N61" s="79"/>
-      <c r="O61" s="79"/>
-      <c r="P61" s="79"/>
-      <c r="Q61" s="59"/>
-      <c r="R61" s="59"/>
-      <c r="S61" s="59"/>
-      <c r="T61" s="61"/>
-    </row>
-    <row r="62" ht="17" customHeight="1">
-      <c r="A62" s="91"/>
-      <c r="B62" s="73">
-        <v>50</v>
-      </c>
-      <c r="C62" s="51">
-        <f>(G50/B62)*(PI()*$G$19*$G$19/4)*100</f>
-        <v>0.9768666709247311</v>
-      </c>
-      <c r="D62" s="54">
-        <f>SQRT((C57/C56)*(C57/C56)+(2*$D$22/$G$19)*(2*$D$22/$G$19)+(0.1/B62)*(0.1/B62))*100</f>
-        <v>6.102067552037567</v>
-      </c>
-      <c r="E62" s="92"/>
-      <c r="F62" t="s" s="63">
+      <c r="G62" s="76">
+        <f>AVERAGE(C60:C62)</f>
+        <v>0.97481329422011453</v>
+      </c>
+      <c r="H62" s="87" t="s">
         <v>53</v>
       </c>
-      <c r="G62" s="82">
-        <f>AVERAGE(C60:C62)</f>
-        <v>0.9748132942201145</v>
-      </c>
-      <c r="H62" t="s" s="93">
-        <v>54</v>
-      </c>
-      <c r="I62" s="83">
+      <c r="I62" s="77">
         <f>AVERAGE(D60:D62)</f>
-        <v>6.109736590192616</v>
-      </c>
-      <c r="J62" s="94"/>
-      <c r="K62" s="95"/>
-      <c r="L62" s="95"/>
-      <c r="M62" s="95"/>
-      <c r="N62" s="95"/>
-      <c r="O62" s="95"/>
-      <c r="P62" s="95"/>
-      <c r="Q62" s="95"/>
-      <c r="R62" s="95"/>
-      <c r="S62" s="95"/>
-      <c r="T62" s="96"/>
+        <v>6.1097365901926155</v>
+      </c>
+      <c r="J62" s="88"/>
+      <c r="K62" s="89"/>
+      <c r="L62" s="89"/>
+      <c r="M62" s="89"/>
+      <c r="N62" s="89"/>
+      <c r="O62" s="89"/>
+      <c r="P62" s="89"/>
+      <c r="Q62" s="89"/>
+      <c r="R62" s="89"/>
+      <c r="S62" s="89"/>
+      <c r="T62" s="90"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -5173,7 +5056,7 @@
     <mergeCell ref="B31:E31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <pageSetup orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
@@ -5181,94 +5064,89 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="14" defaultRowHeight="15.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:IV10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14" defaultRowHeight="16" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14" style="97" customWidth="1"/>
-    <col min="2" max="2" width="14" style="97" customWidth="1"/>
-    <col min="3" max="3" width="14" style="97" customWidth="1"/>
-    <col min="4" max="4" width="14" style="97" customWidth="1"/>
-    <col min="5" max="5" width="14" style="97" customWidth="1"/>
-    <col min="6" max="256" width="14" style="97" customWidth="1"/>
+    <col min="1" max="256" width="14" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.55" customHeight="1">
-      <c r="A1" s="98"/>
-      <c r="B1" s="98"/>
-      <c r="C1" s="98"/>
-      <c r="D1" s="98"/>
-      <c r="E1" s="98"/>
-    </row>
-    <row r="2" ht="16.55" customHeight="1">
-      <c r="A2" s="99"/>
-      <c r="B2" s="100"/>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-    </row>
-    <row r="3" ht="16.35" customHeight="1">
-      <c r="A3" s="102"/>
-      <c r="B3" s="103"/>
-      <c r="C3" s="104"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="104"/>
-    </row>
-    <row r="4" ht="16.35" customHeight="1">
-      <c r="A4" s="102"/>
-      <c r="B4" s="103"/>
-      <c r="C4" s="104"/>
-      <c r="D4" s="104"/>
-      <c r="E4" s="104"/>
-    </row>
-    <row r="5" ht="16.35" customHeight="1">
-      <c r="A5" s="102"/>
-      <c r="B5" s="103"/>
-      <c r="C5" s="104"/>
-      <c r="D5" s="104"/>
-      <c r="E5" s="104"/>
-    </row>
-    <row r="6" ht="16.35" customHeight="1">
-      <c r="A6" s="102"/>
-      <c r="B6" s="103"/>
-      <c r="C6" s="104"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="104"/>
-    </row>
-    <row r="7" ht="16.35" customHeight="1">
-      <c r="A7" s="102"/>
-      <c r="B7" s="103"/>
-      <c r="C7" s="104"/>
-      <c r="D7" s="104"/>
-      <c r="E7" s="104"/>
-    </row>
-    <row r="8" ht="16.35" customHeight="1">
-      <c r="A8" s="102"/>
-      <c r="B8" s="103"/>
-      <c r="C8" s="104"/>
-      <c r="D8" s="104"/>
-      <c r="E8" s="104"/>
-    </row>
-    <row r="9" ht="16.35" customHeight="1">
-      <c r="A9" s="102"/>
-      <c r="B9" s="103"/>
-      <c r="C9" s="104"/>
-      <c r="D9" s="104"/>
-      <c r="E9" s="104"/>
-    </row>
-    <row r="10" ht="16.35" customHeight="1">
-      <c r="A10" s="102"/>
-      <c r="B10" s="103"/>
-      <c r="C10" s="104"/>
-      <c r="D10" s="104"/>
-      <c r="E10" s="104"/>
+    <row r="1" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="91"/>
+      <c r="B1" s="91"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="91"/>
+    </row>
+    <row r="2" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="92"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="94"/>
+      <c r="E2" s="94"/>
+    </row>
+    <row r="3" spans="1:5" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="95"/>
+      <c r="B3" s="96"/>
+      <c r="C3" s="97"/>
+      <c r="D3" s="97"/>
+      <c r="E3" s="97"/>
+    </row>
+    <row r="4" spans="1:5" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="95"/>
+      <c r="B4" s="96"/>
+      <c r="C4" s="97"/>
+      <c r="D4" s="97"/>
+      <c r="E4" s="97"/>
+    </row>
+    <row r="5" spans="1:5" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="95"/>
+      <c r="B5" s="96"/>
+      <c r="C5" s="97"/>
+      <c r="D5" s="97"/>
+      <c r="E5" s="97"/>
+    </row>
+    <row r="6" spans="1:5" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="95"/>
+      <c r="B6" s="96"/>
+      <c r="C6" s="97"/>
+      <c r="D6" s="97"/>
+      <c r="E6" s="97"/>
+    </row>
+    <row r="7" spans="1:5" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="95"/>
+      <c r="B7" s="96"/>
+      <c r="C7" s="97"/>
+      <c r="D7" s="97"/>
+      <c r="E7" s="97"/>
+    </row>
+    <row r="8" spans="1:5" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="95"/>
+      <c r="B8" s="96"/>
+      <c r="C8" s="97"/>
+      <c r="D8" s="97"/>
+      <c r="E8" s="97"/>
+    </row>
+    <row r="9" spans="1:5" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="95"/>
+      <c r="B9" s="96"/>
+      <c r="C9" s="97"/>
+      <c r="D9" s="97"/>
+      <c r="E9" s="97"/>
+    </row>
+    <row r="10" spans="1:5" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="95"/>
+      <c r="B10" s="96"/>
+      <c r="C10" s="97"/>
+      <c r="D10" s="97"/>
+      <c r="E10" s="97"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <pageSetup orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
